--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -149,11 +145,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -181,11 +173,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>PE均值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMA之MAX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>成交量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>成交均量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -667,7 +671,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -829,6 +833,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -838,7 +845,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -999,6 +1006,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1042,7 +1052,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1204,6 +1214,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1213,7 +1226,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1375,6 +1388,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>13918241.906652076</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14227459.764016345</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1417,7 +1433,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1579,6 +1595,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1588,7 +1607,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1750,6 +1769,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4556907.088924652</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4866124.9462889209</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1771,11 +1793,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="342725376"/>
-        <c:axId val="342726912"/>
+        <c:axId val="527706752"/>
+        <c:axId val="527730560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="342725376"/>
+        <c:axId val="527706752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1818,14 +1840,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342726912"/>
+        <c:crossAx val="527730560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="342726912"/>
+        <c:axId val="527730560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1876,7 +1898,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="342725376"/>
+        <c:crossAx val="527706752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2067,7 +2089,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2229,6 +2251,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2248,8 +2273,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="557662208"/>
-        <c:axId val="557656320"/>
+        <c:axId val="522266496"/>
+        <c:axId val="522264960"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2274,7 +2299,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2436,6 +2461,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2445,7 +2473,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2607,6 +2635,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2628,11 +2659,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557652992"/>
-        <c:axId val="557654784"/>
+        <c:axId val="522261632"/>
+        <c:axId val="522263168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557652992"/>
+        <c:axId val="522261632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2675,14 +2706,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557654784"/>
+        <c:crossAx val="522263168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557654784"/>
+        <c:axId val="522263168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2733,12 +2764,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557652992"/>
+        <c:crossAx val="522261632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="557656320"/>
+        <c:axId val="522264960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2775,12 +2806,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557662208"/>
+        <c:crossAx val="522266496"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="557662208"/>
+        <c:axId val="522266496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2789,7 +2820,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="557656320"/>
+        <c:crossAx val="522264960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2968,7 +2999,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3130,6 +3161,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3139,7 +3173,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3300,6 +3334,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3343,7 +3380,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3505,6 +3542,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3514,7 +3554,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3676,6 +3716,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>125903856.40114608</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>128762636.16003911</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3718,7 +3761,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3880,6 +3923,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3889,7 +3935,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4051,6 +4097,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>48489150.250258386</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>51347930.009151414</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4072,11 +4121,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557693952"/>
-        <c:axId val="557695744"/>
+        <c:axId val="522658944"/>
+        <c:axId val="522660480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557693952"/>
+        <c:axId val="522658944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4119,14 +4168,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557695744"/>
+        <c:crossAx val="522660480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557695744"/>
+        <c:axId val="522660480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4226,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557693952"/>
+        <c:crossAx val="522658944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4368,7 +4417,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4530,6 +4579,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-73556.079313855051</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-244188.52262430632</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4549,8 +4601,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="558043520"/>
-        <c:axId val="558041728"/>
+        <c:axId val="522684672"/>
+        <c:axId val="522683136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4575,7 +4627,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4737,6 +4789,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4746,7 +4801,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4908,6 +4963,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4929,11 +4987,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557710720"/>
-        <c:axId val="558040192"/>
+        <c:axId val="522679808"/>
+        <c:axId val="522681344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557710720"/>
+        <c:axId val="522679808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4976,14 +5034,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558040192"/>
+        <c:crossAx val="522681344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558040192"/>
+        <c:axId val="522681344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5034,12 +5092,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557710720"/>
+        <c:crossAx val="522679808"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="558041728"/>
+        <c:axId val="522683136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5076,12 +5134,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558043520"/>
+        <c:crossAx val="522684672"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="558043520"/>
+        <c:axId val="522684672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5090,7 +5148,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="558041728"/>
+        <c:crossAx val="522683136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5269,7 +5327,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5431,6 +5489,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5440,7 +5501,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5601,6 +5662,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5644,7 +5708,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5806,6 +5870,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5815,7 +5882,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5977,6 +6044,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>123495447.62582658</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>126271503.9026759</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6019,7 +6089,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6181,6 +6251,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6190,7 +6263,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6352,6 +6425,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>41723610.151589885</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>44499666.4284392</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6373,11 +6449,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560577920"/>
-        <c:axId val="560596096"/>
+        <c:axId val="522712960"/>
+        <c:axId val="522714496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560577920"/>
+        <c:axId val="522712960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6420,14 +6496,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560596096"/>
+        <c:crossAx val="522714496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560596096"/>
+        <c:axId val="522714496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6478,7 +6554,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560577920"/>
+        <c:crossAx val="522712960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6669,7 +6745,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6831,6 +6907,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-255103.75807364078</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-575981.71600752324</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6850,8 +6929,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="560661248"/>
-        <c:axId val="560647168"/>
+        <c:axId val="522882048"/>
+        <c:axId val="522880512"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6876,7 +6955,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7038,6 +7117,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7047,7 +7129,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7209,6 +7291,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7230,11 +7315,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560644096"/>
-        <c:axId val="560645632"/>
+        <c:axId val="522868992"/>
+        <c:axId val="522878976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560644096"/>
+        <c:axId val="522868992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7277,14 +7362,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560645632"/>
+        <c:crossAx val="522878976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560645632"/>
+        <c:axId val="522878976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7335,12 +7420,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560644096"/>
+        <c:crossAx val="522868992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="560647168"/>
+        <c:axId val="522880512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7377,12 +7462,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="560661248"/>
+        <c:crossAx val="522882048"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="560661248"/>
+        <c:axId val="522882048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7391,7 +7476,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="560647168"/>
+        <c:crossAx val="522880512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7553,7 +7638,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7715,6 +7800,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7734,8 +7822,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="558062208"/>
-        <c:axId val="558059904"/>
+        <c:axId val="676407936"/>
+        <c:axId val="676406400"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7760,7 +7848,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7922,6 +8010,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7931,7 +8022,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8093,6 +8184,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8114,11 +8208,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558056192"/>
-        <c:axId val="558058112"/>
+        <c:axId val="670754304"/>
+        <c:axId val="670756224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558056192"/>
+        <c:axId val="670754304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8161,14 +8255,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558058112"/>
+        <c:crossAx val="670756224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558058112"/>
+        <c:axId val="670756224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8219,12 +8313,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558056192"/>
+        <c:crossAx val="670754304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="558059904"/>
+        <c:axId val="676406400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8261,12 +8355,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558062208"/>
+        <c:crossAx val="676407936"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="558062208"/>
+        <c:axId val="676407936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8275,7 +8369,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="558059904"/>
+        <c:crossAx val="676406400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8454,7 +8548,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8616,6 +8710,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8625,7 +8722,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8786,6 +8883,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -8829,7 +8929,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8991,6 +9091,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9000,7 +9103,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9162,6 +9265,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>16004082.547668742</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>16362949.816239173</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9204,7 +9310,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9366,6 +9472,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9375,7 +9484,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9537,6 +9646,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>5116246.7741877642</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5475114.0427581947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9558,11 +9670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566559872"/>
-        <c:axId val="566567680"/>
+        <c:axId val="676450688"/>
+        <c:axId val="676452224"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566559872"/>
+        <c:axId val="676450688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9605,14 +9717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566567680"/>
+        <c:crossAx val="676452224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566567680"/>
+        <c:axId val="676452224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9663,7 +9775,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566559872"/>
+        <c:crossAx val="676450688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9875,7 +9987,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10037,6 +10149,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-21886.088907832516</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10056,8 +10171,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566717056"/>
-        <c:axId val="566715136"/>
+        <c:axId val="684151936"/>
+        <c:axId val="684125568"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10082,7 +10197,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10244,6 +10359,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10253,7 +10371,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10415,6 +10533,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10436,11 +10557,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566703232"/>
-        <c:axId val="566705152"/>
+        <c:axId val="684108800"/>
+        <c:axId val="684122880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566703232"/>
+        <c:axId val="684108800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10483,14 +10604,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566705152"/>
+        <c:crossAx val="684122880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566705152"/>
+        <c:axId val="684122880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10541,12 +10662,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566703232"/>
+        <c:crossAx val="684108800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="566715136"/>
+        <c:axId val="684125568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10583,12 +10704,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566717056"/>
+        <c:crossAx val="684151936"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566717056"/>
+        <c:axId val="684151936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10597,7 +10718,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="566715136"/>
+        <c:crossAx val="684125568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10776,7 +10897,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10938,6 +11059,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10947,7 +11071,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11108,6 +11232,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11151,7 +11278,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11313,6 +11440,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11322,7 +11452,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11484,6 +11614,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>143601687.95709997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>146848513.50795704</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11526,7 +11659,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11688,6 +11821,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11697,7 +11833,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11859,6 +11995,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>47453227.12889497</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>50700052.679752037</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11880,11 +12019,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567398400"/>
-        <c:axId val="567399936"/>
+        <c:axId val="684375424"/>
+        <c:axId val="684542208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567398400"/>
+        <c:axId val="684375424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11927,14 +12066,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567399936"/>
+        <c:crossAx val="684542208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="567399936"/>
+        <c:axId val="684542208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11985,7 +12124,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567398400"/>
+        <c:crossAx val="684375424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12197,7 +12336,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12359,6 +12498,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-255103.75807364078</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-115196.34320150466</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12378,8 +12520,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="567831936"/>
-        <c:axId val="567830016"/>
+        <c:axId val="685246720"/>
+        <c:axId val="684705664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12404,7 +12546,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12566,6 +12708,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12575,7 +12720,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12737,6 +12882,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12758,11 +12906,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="567806208"/>
-        <c:axId val="567828480"/>
+        <c:axId val="684685568"/>
+        <c:axId val="684703744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="567806208"/>
+        <c:axId val="684685568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12805,14 +12953,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567828480"/>
+        <c:crossAx val="684703744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="567828480"/>
+        <c:axId val="684703744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12863,12 +13011,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567806208"/>
+        <c:crossAx val="684685568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="567830016"/>
+        <c:axId val="684705664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12905,12 +13053,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="567831936"/>
+        <c:crossAx val="685246720"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="567831936"/>
+        <c:axId val="685246720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12919,7 +13067,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="567830016"/>
+        <c:crossAx val="684705664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13098,7 +13246,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13260,6 +13408,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13269,7 +13420,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13430,6 +13581,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -13473,7 +13627,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13635,6 +13789,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13644,7 +13801,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13806,6 +13963,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>20076636.585374579</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>20534328.477339741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13848,7 +14008,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14010,6 +14170,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14019,7 +14182,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14181,6 +14344,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>7674340.1054448206</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>8132031.9974099826</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14202,11 +14368,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568066816"/>
-        <c:axId val="568165120"/>
+        <c:axId val="721496704"/>
+        <c:axId val="746365312"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568066816"/>
+        <c:axId val="721496704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14249,14 +14415,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568165120"/>
+        <c:crossAx val="746365312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="568165120"/>
+        <c:axId val="746365312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14307,7 +14473,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568066816"/>
+        <c:crossAx val="721496704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14498,7 +14664,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14660,6 +14826,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>-10241.985727245639</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-6800.1867059933402</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14679,8 +14848,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="475340160"/>
-        <c:axId val="475338624"/>
+        <c:axId val="521987584"/>
+        <c:axId val="521986048"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14705,7 +14874,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14867,6 +15036,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14876,7 +15048,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15038,6 +15210,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>1.0399999618530273</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0640000104904175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15059,11 +15234,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475335296"/>
-        <c:axId val="475337088"/>
+        <c:axId val="521982720"/>
+        <c:axId val="521984256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475335296"/>
+        <c:axId val="521982720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15106,14 +15281,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475337088"/>
+        <c:crossAx val="521984256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475337088"/>
+        <c:axId val="521984256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15164,12 +15339,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475335296"/>
+        <c:crossAx val="521982720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="475338624"/>
+        <c:axId val="521986048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15206,12 +15381,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475340160"/>
+        <c:crossAx val="521987584"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="475340160"/>
+        <c:axId val="521987584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15220,7 +15395,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="475338624"/>
+        <c:crossAx val="521986048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15399,7 +15574,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15561,6 +15736,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15570,7 +15748,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15731,6 +15909,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="53">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -15774,7 +15955,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15936,6 +16117,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15945,7 +16129,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16107,6 +16291,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>14206131.613092119</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>14521993.092773886</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16149,7 +16336,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16311,6 +16498,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16320,7 +16510,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="54"/>
+                <c:ptCount val="55"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16482,6 +16672,9 @@
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>4672062.0345211513</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4987923.5142029189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16503,11 +16696,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556825216"/>
-        <c:axId val="557187456"/>
+        <c:axId val="522175232"/>
+        <c:axId val="522176768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556825216"/>
+        <c:axId val="522175232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16550,14 +16743,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557187456"/>
+        <c:crossAx val="522176768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557187456"/>
+        <c:axId val="522176768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16608,7 +16801,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556825216"/>
+        <c:crossAx val="522175232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17544,7 +17737,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -17675,28 +17868,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -19957,6 +20150,44 @@
       </c>
       <c r="L56" s="29">
         <v>518829.06704185653</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="32">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="31">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="29">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="29">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="30">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="30">
+        <v>12781203.118754858</v>
+      </c>
+      <c r="H57" s="30">
+        <v>13599200.252435327</v>
+      </c>
+      <c r="I57" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J57" s="30">
+        <v>14227459.764016345</v>
+      </c>
+      <c r="K57" s="30">
+        <v>4866124.9462889209</v>
+      </c>
+      <c r="L57" s="29">
+        <v>628259.51158101915</v>
       </c>
     </row>
   </sheetData>
@@ -19975,7 +20206,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20010,16 +20241,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20046,16 +20277,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="P1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20117,28 +20348,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23017,6 +23248,56 @@
       </c>
       <c r="P56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-21886.088907832516</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-20569.632229368879</v>
+      </c>
+      <c r="G57" s="18">
+        <v>14932202.922212096</v>
+      </c>
+      <c r="H57" s="18">
+        <v>15887864.065878714</v>
+      </c>
+      <c r="I57" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J57" s="18">
+        <v>16362949.816239173</v>
+      </c>
+      <c r="K57" s="18">
+        <v>5475114.0427581947</v>
+      </c>
+      <c r="L57" s="17">
+        <v>475085.75036045833</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -23035,7 +23316,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH56"/>
+  <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23070,16 +23351,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23106,16 +23387,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="P1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="O1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -23177,28 +23458,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26077,6 +26358,56 @@
       </c>
       <c r="P56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-115196.34320150466</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-108267.23878358658</v>
+      </c>
+      <c r="G57" s="18">
+        <v>135175856.55248034</v>
+      </c>
+      <c r="H57" s="18">
+        <v>143827112.78989026</v>
+      </c>
+      <c r="I57" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J57" s="18">
+        <v>146848513.50795704</v>
+      </c>
+      <c r="K57" s="18">
+        <v>50700052.679752037</v>
+      </c>
+      <c r="L57" s="17">
+        <v>3021400.7180667794</v>
+      </c>
+      <c r="M57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="N57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="O57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -26095,7 +26426,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26130,16 +26461,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -26172,16 +26503,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="R1" s="11" t="s">
         <v>23</v>
-      </c>
-      <c r="Q1" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -26255,28 +26586,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -29473,6 +29804,62 @@
       </c>
       <c r="R56" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-6800.1867059933402</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-6391.1528561536452</v>
+      </c>
+      <c r="I57" s="18">
+        <v>19064065.698306736</v>
+      </c>
+      <c r="J57" s="18">
+        <v>20284166.102988373</v>
+      </c>
+      <c r="K57" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L57" s="18">
+        <v>20534328.477339741</v>
+      </c>
+      <c r="M57" s="18">
+        <v>8132031.9974099826</v>
+      </c>
+      <c r="N57" s="17">
+        <v>250162.37435136616</v>
+      </c>
+      <c r="O57" s="22">
+        <v>3.2977829855092559E-2</v>
+      </c>
+      <c r="P57" s="22">
+        <v>4.2461169415320556E-2</v>
+      </c>
+      <c r="Q57" s="22">
+        <v>77.665854024250493</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -29491,7 +29878,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29526,16 +29913,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -29562,19 +29949,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -29652,28 +30039,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -32713,6 +33100,59 @@
         <v>83.790672900129579</v>
       </c>
       <c r="Q56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-102848.16114684439</v>
+      </c>
+      <c r="G57" s="18">
+        <v>13058020.154331565</v>
+      </c>
+      <c r="H57" s="18">
+        <v>13893733.581192868</v>
+      </c>
+      <c r="I57" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J57" s="18">
+        <v>14521993.092773886</v>
+      </c>
+      <c r="K57" s="18">
+        <v>4987923.5142029189</v>
+      </c>
+      <c r="L57" s="17">
+        <v>628259.51158101915</v>
+      </c>
+      <c r="M57" s="21">
+        <v>82.317072210415034</v>
+      </c>
+      <c r="N57" s="21">
+        <v>82.130142596708495</v>
+      </c>
+      <c r="O57" s="21">
+        <v>81.483167688714857</v>
+      </c>
+      <c r="P57" s="21">
+        <v>83.424092412695785</v>
+      </c>
+      <c r="Q57" s="1">
         <v>1</v>
       </c>
     </row>
@@ -32732,7 +33172,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -32773,10 +33213,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -32878,28 +33318,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -35478,6 +35918,50 @@
       </c>
       <c r="N56" s="17">
         <v>2023655.7767591949</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>1780809</v>
+      </c>
+      <c r="F57" s="17">
+        <v>4200498.0933511853</v>
+      </c>
+      <c r="G57" s="17">
+        <v>-244188.52262430632</v>
+      </c>
+      <c r="H57" s="18">
+        <v>-229500.48892551727</v>
+      </c>
+      <c r="I57" s="18">
+        <v>118886081.40365693</v>
+      </c>
+      <c r="J57" s="18">
+        <v>126494791.86065561</v>
+      </c>
+      <c r="K57" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L57" s="18">
+        <v>128762636.16003911</v>
+      </c>
+      <c r="M57" s="18">
+        <v>51347930.009151414</v>
+      </c>
+      <c r="N57" s="17">
+        <v>2267844.2993835011</v>
       </c>
     </row>
   </sheetData>
@@ -35496,7 +35980,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -35531,16 +36015,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -35627,28 +36111,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -37909,6 +38393,44 @@
       </c>
       <c r="L56" s="17">
         <v>3199923.827292583</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A57" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B57" s="31">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C57" s="16">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D57" s="17">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E57" s="17">
+        <v>-575981.71600752324</v>
+      </c>
+      <c r="F57" s="18">
+        <v>-541336.19391793292</v>
+      </c>
+      <c r="G57" s="18">
+        <v>115127440.93199331</v>
+      </c>
+      <c r="H57" s="18">
+        <v>122495598.35937579</v>
+      </c>
+      <c r="I57" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J57" s="18">
+        <v>126271503.9026759</v>
+      </c>
+      <c r="K57" s="18">
+        <v>44499666.4284392</v>
+      </c>
+      <c r="L57" s="17">
+        <v>3775905.5433001062</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -145,7 +149,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -169,14 +177,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -186,10 +186,6 @@
   </si>
   <si>
     <t>成交均量</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -671,7 +667,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -836,6 +832,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -845,7 +844,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1009,6 +1008,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1052,7 +1054,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1217,6 +1219,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1226,7 +1231,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1391,6 +1396,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14227459.764016345</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14329709.596181171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1433,7 +1441,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1598,6 +1606,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1607,7 +1618,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1772,6 +1783,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4866124.9462889209</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4968374.7784537468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1793,11 +1807,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527706752"/>
-        <c:axId val="527730560"/>
+        <c:axId val="563943296"/>
+        <c:axId val="563944832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527706752"/>
+        <c:axId val="563943296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1840,14 +1854,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527730560"/>
+        <c:crossAx val="563944832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527730560"/>
+        <c:axId val="563944832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1898,7 +1912,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527706752"/>
+        <c:crossAx val="563943296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2089,7 +2103,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2254,6 +2268,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2273,8 +2290,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522266496"/>
-        <c:axId val="522264960"/>
+        <c:axId val="614385152"/>
+        <c:axId val="614383616"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2299,7 +2316,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2464,6 +2481,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2473,7 +2493,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2638,6 +2658,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2659,11 +2682,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522261632"/>
-        <c:axId val="522263168"/>
+        <c:axId val="611914496"/>
+        <c:axId val="611916032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522261632"/>
+        <c:axId val="611914496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2706,14 +2729,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522263168"/>
+        <c:crossAx val="611916032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522263168"/>
+        <c:axId val="611916032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2764,12 +2787,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522261632"/>
+        <c:crossAx val="611914496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522264960"/>
+        <c:axId val="614383616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2806,12 +2829,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522266496"/>
+        <c:crossAx val="614385152"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522266496"/>
+        <c:axId val="614385152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2820,7 +2843,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522264960"/>
+        <c:crossAx val="614383616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2999,7 +3022,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3164,6 +3187,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3173,7 +3199,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3337,6 +3363,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3380,7 +3409,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3545,6 +3574,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3554,7 +3586,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3719,6 +3751,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>128762636.16003911</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>129713726.73870459</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3761,7 +3796,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3926,6 +3961,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3935,7 +3973,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4100,6 +4138,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>51347930.009151414</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>52299020.587816894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4121,11 +4162,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522658944"/>
-        <c:axId val="522660480"/>
+        <c:axId val="615924480"/>
+        <c:axId val="615926016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522658944"/>
+        <c:axId val="615924480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4168,14 +4209,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522660480"/>
+        <c:crossAx val="615926016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522660480"/>
+        <c:axId val="615926016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4226,7 +4267,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522658944"/>
+        <c:crossAx val="615924480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4417,7 +4458,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4582,6 +4623,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-244188.52262430632</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-637497.67999171233</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4601,8 +4645,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522684672"/>
-        <c:axId val="522683136"/>
+        <c:axId val="615954304"/>
+        <c:axId val="615952768"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4627,7 +4671,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4792,6 +4836,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4801,7 +4848,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -4966,6 +5013,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4987,11 +5037,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522679808"/>
-        <c:axId val="522681344"/>
+        <c:axId val="615949440"/>
+        <c:axId val="615950976"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522679808"/>
+        <c:axId val="615949440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5034,14 +5084,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522681344"/>
+        <c:crossAx val="615950976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522681344"/>
+        <c:axId val="615950976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5092,12 +5142,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522679808"/>
+        <c:crossAx val="615949440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522683136"/>
+        <c:axId val="615952768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5134,12 +5184,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522684672"/>
+        <c:crossAx val="615954304"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522684672"/>
+        <c:axId val="615954304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5148,7 +5198,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522683136"/>
+        <c:crossAx val="615952768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5327,7 +5377,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5492,6 +5542,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5501,7 +5554,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5665,6 +5718,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5708,7 +5764,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5873,6 +5929,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5882,7 +5941,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6047,6 +6106,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>126271503.9026759</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>127192525.29663128</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6089,7 +6151,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6254,6 +6316,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6263,7 +6328,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6428,6 +6493,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>44499666.4284392</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>45420687.82239458</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6449,11 +6517,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522712960"/>
-        <c:axId val="522714496"/>
+        <c:axId val="616023168"/>
+        <c:axId val="616024704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522712960"/>
+        <c:axId val="616023168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6496,14 +6564,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522714496"/>
+        <c:crossAx val="616024704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522714496"/>
+        <c:axId val="616024704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6554,7 +6622,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522712960"/>
+        <c:crossAx val="616023168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6745,7 +6813,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6910,6 +6978,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-575981.71600752324</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-745710.74747990887</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6929,8 +7000,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="522882048"/>
-        <c:axId val="522880512"/>
+        <c:axId val="616511744"/>
+        <c:axId val="616510208"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6955,7 +7026,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7120,6 +7191,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7129,7 +7203,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7294,6 +7368,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7315,11 +7392,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522868992"/>
-        <c:axId val="522878976"/>
+        <c:axId val="616506880"/>
+        <c:axId val="616508416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522868992"/>
+        <c:axId val="616506880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7362,14 +7439,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522878976"/>
+        <c:crossAx val="616508416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522878976"/>
+        <c:axId val="616508416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7420,12 +7497,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522868992"/>
+        <c:crossAx val="616506880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="522880512"/>
+        <c:axId val="616510208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7462,12 +7539,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522882048"/>
+        <c:crossAx val="616511744"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="522882048"/>
+        <c:axId val="616511744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7476,7 +7553,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="522880512"/>
+        <c:crossAx val="616510208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7638,7 +7715,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7803,6 +7880,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7822,8 +7902,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="676407936"/>
-        <c:axId val="676406400"/>
+        <c:axId val="617980288"/>
+        <c:axId val="617978496"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7848,7 +7928,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8013,6 +8093,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8022,7 +8105,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8187,6 +8270,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8208,11 +8294,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="670754304"/>
-        <c:axId val="670756224"/>
+        <c:axId val="617974016"/>
+        <c:axId val="617976192"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="670754304"/>
+        <c:axId val="617974016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8255,14 +8341,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670756224"/>
+        <c:crossAx val="617976192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="670756224"/>
+        <c:axId val="617976192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8313,12 +8399,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="670754304"/>
+        <c:crossAx val="617974016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="676406400"/>
+        <c:axId val="617978496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8355,12 +8441,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676407936"/>
+        <c:crossAx val="617980288"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="676407936"/>
+        <c:axId val="617980288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8369,7 +8455,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="676406400"/>
+        <c:crossAx val="617978496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8548,7 +8634,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8713,6 +8799,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8722,7 +8811,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8886,6 +8975,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -8929,7 +9021,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9094,6 +9186,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9103,7 +9198,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9268,6 +9363,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>16362949.816239173</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>16482407.681704661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9310,7 +9408,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9475,6 +9573,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9484,7 +9585,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9649,6 +9750,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>5475114.0427581947</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5594571.908223683</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9670,11 +9774,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="676450688"/>
-        <c:axId val="676452224"/>
+        <c:axId val="617994112"/>
+        <c:axId val="617995648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="676450688"/>
+        <c:axId val="617994112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9717,14 +9821,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676452224"/>
+        <c:crossAx val="617995648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="676452224"/>
+        <c:axId val="617995648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9775,7 +9879,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676450688"/>
+        <c:crossAx val="617994112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9987,7 +10091,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10152,6 +10256,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-21886.088907832516</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-25998.161012664015</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10171,8 +10278,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="684151936"/>
-        <c:axId val="684125568"/>
+        <c:axId val="621659264"/>
+        <c:axId val="621579648"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10197,7 +10304,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10362,6 +10469,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10371,7 +10481,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10536,6 +10646,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10557,11 +10670,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="684108800"/>
-        <c:axId val="684122880"/>
+        <c:axId val="621558784"/>
+        <c:axId val="621576960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="684108800"/>
+        <c:axId val="621558784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10604,14 +10717,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684122880"/>
+        <c:crossAx val="621576960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="684122880"/>
+        <c:axId val="621576960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10662,12 +10775,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684108800"/>
+        <c:crossAx val="621558784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="684125568"/>
+        <c:axId val="621579648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10704,12 +10817,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684151936"/>
+        <c:crossAx val="621659264"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="684151936"/>
+        <c:axId val="621659264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10718,7 +10831,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="684125568"/>
+        <c:crossAx val="621579648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10897,7 +11010,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11062,6 +11175,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11071,7 +11187,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11235,6 +11351,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11278,7 +11397,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11443,6 +11562,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11452,7 +11574,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11617,6 +11739,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>146848513.50795704</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>147929922.55191049</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11659,7 +11784,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11824,6 +11949,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11833,7 +11961,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11998,6 +12126,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>50700052.679752037</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>51781461.723705485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12019,11 +12150,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="684375424"/>
-        <c:axId val="684542208"/>
+        <c:axId val="623556864"/>
+        <c:axId val="624558080"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="684375424"/>
+        <c:axId val="623556864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12066,14 +12197,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684542208"/>
+        <c:crossAx val="624558080"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="684542208"/>
+        <c:axId val="624558080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12124,7 +12255,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684375424"/>
+        <c:crossAx val="623556864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12336,7 +12467,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12501,6 +12632,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-115196.34320150466</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-149142.14949598178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12520,8 +12654,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="685246720"/>
-        <c:axId val="684705664"/>
+        <c:axId val="625399680"/>
+        <c:axId val="625398144"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12546,7 +12680,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12711,6 +12845,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12720,7 +12857,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -12885,6 +13022,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12906,11 +13046,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="684685568"/>
-        <c:axId val="684703744"/>
+        <c:axId val="625374336"/>
+        <c:axId val="625375872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="684685568"/>
+        <c:axId val="625374336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12953,14 +13093,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684703744"/>
+        <c:crossAx val="625375872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="684703744"/>
+        <c:axId val="625375872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13011,12 +13151,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684685568"/>
+        <c:crossAx val="625374336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="684705664"/>
+        <c:axId val="625398144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13053,12 +13193,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="685246720"/>
+        <c:crossAx val="625399680"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="685246720"/>
+        <c:axId val="625399680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13067,7 +13207,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="684705664"/>
+        <c:crossAx val="625398144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13246,7 +13386,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13411,6 +13551,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13420,7 +13563,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13584,6 +13727,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -13627,7 +13773,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13792,6 +13938,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13801,7 +13950,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13966,6 +14115,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>20534328.477339741</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>20686841.312001664</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14008,7 +14160,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14173,6 +14325,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14182,7 +14337,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14347,6 +14502,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>8132031.9974099826</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>8284544.832071906</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14368,11 +14526,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="721496704"/>
-        <c:axId val="746365312"/>
+        <c:axId val="625568768"/>
+        <c:axId val="625570560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="721496704"/>
+        <c:axId val="625568768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14415,14 +14573,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="746365312"/>
+        <c:crossAx val="625570560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="746365312"/>
+        <c:axId val="625570560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14473,7 +14631,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="721496704"/>
+        <c:crossAx val="625568768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14664,7 +14822,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14829,6 +14987,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>-6800.1867059933402</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-17753.099949136293</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14848,8 +15009,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="521987584"/>
-        <c:axId val="521986048"/>
+        <c:axId val="625970560"/>
+        <c:axId val="625969024"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -14874,7 +15035,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15039,6 +15200,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15048,7 +15212,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15213,6 +15377,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>1.0640000104904175</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.0720000267028809</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15234,11 +15401,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521982720"/>
-        <c:axId val="521984256"/>
+        <c:axId val="625846528"/>
+        <c:axId val="625967104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521982720"/>
+        <c:axId val="625846528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15281,14 +15448,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521984256"/>
+        <c:crossAx val="625967104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521984256"/>
+        <c:axId val="625967104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15339,12 +15506,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521982720"/>
+        <c:crossAx val="625846528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="521986048"/>
+        <c:axId val="625969024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15381,12 +15548,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521987584"/>
+        <c:crossAx val="625970560"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="521987584"/>
+        <c:axId val="625970560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15395,7 +15562,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="521986048"/>
+        <c:crossAx val="625969024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15574,7 +15741,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15739,6 +15906,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15748,7 +15918,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15912,6 +16082,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="54">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -15955,7 +16128,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16120,6 +16293,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16129,7 +16305,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16294,6 +16470,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>14521993.092773886</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>14626457.465711212</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16336,7 +16515,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16501,6 +16680,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16510,7 +16692,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="55"/>
+                <c:ptCount val="56"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16675,6 +16857,9 @@
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>4987923.5142029189</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5092387.8871402442</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16696,11 +16881,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522175232"/>
-        <c:axId val="522176768"/>
+        <c:axId val="568107392"/>
+        <c:axId val="568108928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522175232"/>
+        <c:axId val="568107392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16743,14 +16928,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522176768"/>
+        <c:crossAx val="568108928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="522176768"/>
+        <c:axId val="568108928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16801,7 +16986,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522175232"/>
+        <c:crossAx val="568107392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16902,7 +17087,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16940,7 +17125,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16983,7 +17168,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17021,7 +17206,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17064,7 +17249,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17102,7 +17287,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17145,7 +17330,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17183,7 +17368,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17226,7 +17411,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17264,7 +17449,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17307,7 +17492,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17345,7 +17530,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17388,7 +17573,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17426,7 +17611,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17737,7 +17922,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -17868,28 +18053,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20188,6 +20373,44 @@
       </c>
       <c r="L57" s="29">
         <v>628259.51158101915</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="32">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="31">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="29">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="29">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="30">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="30">
+        <v>12659943.042425262</v>
+      </c>
+      <c r="H58" s="30">
+        <v>13571459.279536832</v>
+      </c>
+      <c r="I58" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J58" s="30">
+        <v>14329709.596181171</v>
+      </c>
+      <c r="K58" s="30">
+        <v>4968374.7784537468</v>
+      </c>
+      <c r="L58" s="29">
+        <v>758250.31664433924</v>
       </c>
     </row>
   </sheetData>
@@ -20206,7 +20429,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20241,16 +20464,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20277,16 +20500,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20348,28 +20571,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23297,6 +23520,56 @@
         <v>77.665854024250493</v>
       </c>
       <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-25998.161012664015</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-24252.015265919163</v>
+      </c>
+      <c r="G58" s="18">
+        <v>14907950.906946177</v>
+      </c>
+      <c r="H58" s="18">
+        <v>15981323.770331539</v>
+      </c>
+      <c r="I58" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J58" s="18">
+        <v>16482407.681704661</v>
+      </c>
+      <c r="K58" s="18">
+        <v>5594571.908223683</v>
+      </c>
+      <c r="L58" s="17">
+        <v>501083.91137312236</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23316,7 +23589,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH57"/>
+  <dimension ref="A1:AH58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23351,16 +23624,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23390,13 +23663,13 @@
         <v>26</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -23458,28 +23731,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26407,6 +26680,56 @@
         <v>77.665854024250493</v>
       </c>
       <c r="P57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-149142.14949598178</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-139125.13598968269</v>
+      </c>
+      <c r="G58" s="18">
+        <v>135036731.41649064</v>
+      </c>
+      <c r="H58" s="18">
+        <v>144759379.68434772</v>
+      </c>
+      <c r="I58" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J58" s="18">
+        <v>147929922.55191049</v>
+      </c>
+      <c r="K58" s="18">
+        <v>51781461.723705485</v>
+      </c>
+      <c r="L58" s="17">
+        <v>3170542.8675627611</v>
+      </c>
+      <c r="M58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="N58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="O58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="P58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -26426,7 +26749,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26461,16 +26784,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -26503,16 +26826,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -26586,28 +26909,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -29859,6 +30182,62 @@
         <v>77.665854024250493</v>
       </c>
       <c r="R57" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-17753.099949136293</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-16560.72715197497</v>
+      </c>
+      <c r="I58" s="18">
+        <v>19047504.971154761</v>
+      </c>
+      <c r="J58" s="18">
+        <v>20418925.83770116</v>
+      </c>
+      <c r="K58" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L58" s="18">
+        <v>20686841.312001664</v>
+      </c>
+      <c r="M58" s="18">
+        <v>8284544.832071906</v>
+      </c>
+      <c r="N58" s="17">
+        <v>267915.47430050245</v>
+      </c>
+      <c r="O58" s="22">
+        <v>2.8814860914654364E-2</v>
+      </c>
+      <c r="P58" s="22">
+        <v>3.6717643881511025E-2</v>
+      </c>
+      <c r="Q58" s="22">
+        <v>78.476878875019352</v>
+      </c>
+      <c r="R58" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -29878,7 +30257,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -29913,16 +30292,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>24</v>
-      </c>
       <c r="D1" s="14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -29949,19 +30328,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="O1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="Q1" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30039,28 +30418,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -33153,6 +33532,59 @@
         <v>83.424092412695785</v>
       </c>
       <c r="Q57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-121260.07632959579</v>
+      </c>
+      <c r="G58" s="18">
+        <v>12936760.078001969</v>
+      </c>
+      <c r="H58" s="18">
+        <v>13868207.149066873</v>
+      </c>
+      <c r="I58" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J58" s="18">
+        <v>14626457.465711212</v>
+      </c>
+      <c r="K58" s="18">
+        <v>5092387.8871402442</v>
+      </c>
+      <c r="L58" s="17">
+        <v>758250.31664433924</v>
+      </c>
+      <c r="M58" s="21">
+        <v>79.155674275563754</v>
+      </c>
+      <c r="N58" s="21">
+        <v>81.138653156326924</v>
+      </c>
+      <c r="O58" s="21">
+        <v>81.368329511252213</v>
+      </c>
+      <c r="P58" s="21">
+        <v>80.679300446476333</v>
+      </c>
+      <c r="Q58" s="1">
         <v>1</v>
       </c>
     </row>
@@ -33172,7 +33604,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ57"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33207,16 +33639,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>27</v>
@@ -33318,28 +33750,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -35962,6 +36394,50 @@
       </c>
       <c r="N57" s="17">
         <v>2267844.2993835011</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3570901.25</v>
+      </c>
+      <c r="F58" s="17">
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="G58" s="17">
+        <v>-637497.67999171233</v>
+      </c>
+      <c r="H58" s="18">
+        <v>-594680.65682091936</v>
+      </c>
+      <c r="I58" s="18">
+        <v>118291400.74683601</v>
+      </c>
+      <c r="J58" s="18">
+        <v>126808384.75932938</v>
+      </c>
+      <c r="K58" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L58" s="18">
+        <v>129713726.73870459</v>
+      </c>
+      <c r="M58" s="18">
+        <v>52299020.587816894</v>
+      </c>
+      <c r="N58" s="17">
+        <v>2905341.9793752134</v>
       </c>
     </row>
   </sheetData>
@@ -35980,7 +36456,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36015,16 +36491,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -36111,28 +36587,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -38431,6 +38907,44 @@
       </c>
       <c r="L57" s="17">
         <v>3775905.5433001062</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A58" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B58" s="31">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C58" s="16">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D58" s="17">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E58" s="17">
+        <v>-745710.74747990887</v>
+      </c>
+      <c r="F58" s="18">
+        <v>-695625.6799484134</v>
+      </c>
+      <c r="G58" s="18">
+        <v>114431815.25204489</v>
+      </c>
+      <c r="H58" s="18">
+        <v>122670909.00585125</v>
+      </c>
+      <c r="I58" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J58" s="18">
+        <v>127192525.29663128</v>
+      </c>
+      <c r="K58" s="18">
+        <v>45420687.82239458</v>
+      </c>
+      <c r="L58" s="17">
+        <v>4521616.2907800153</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -137,7 +133,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>总资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>盈利金额</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>回收资金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -149,11 +153,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -177,7 +177,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SMA之MAX</t>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -606,7 +614,7 @@
               </a:rPr>
               <a:t>）</a:t>
             </a:r>
-            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -667,7 +675,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -835,6 +843,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,7 +855,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1011,6 +1022,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1054,7 +1068,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1222,6 +1236,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1231,7 +1248,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1399,6 +1416,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14329709.596181171</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14367689.690924622</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1441,7 +1461,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1609,6 +1629,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1618,7 +1641,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1786,6 +1809,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4968374.7784537468</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5006354.8731971979</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1807,11 +1833,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="563943296"/>
-        <c:axId val="563944832"/>
+        <c:axId val="391471488"/>
+        <c:axId val="391473408"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="563943296"/>
+        <c:axId val="391471488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1854,14 +1880,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563944832"/>
+        <c:crossAx val="391473408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="563944832"/>
+        <c:axId val="391473408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1912,7 +1938,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563943296"/>
+        <c:crossAx val="391471488"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2103,7 +2129,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2271,6 +2297,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2290,8 +2319,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="614385152"/>
-        <c:axId val="614383616"/>
+        <c:axId val="431670784"/>
+        <c:axId val="431669248"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2316,7 +2345,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2484,6 +2513,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2493,7 +2525,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2661,6 +2693,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2682,11 +2717,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="611914496"/>
-        <c:axId val="611916032"/>
+        <c:axId val="392872704"/>
+        <c:axId val="392874240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="611914496"/>
+        <c:axId val="392872704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2729,14 +2764,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611916032"/>
+        <c:crossAx val="392874240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="611916032"/>
+        <c:axId val="392874240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2787,12 +2822,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="611914496"/>
+        <c:crossAx val="392872704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="614383616"/>
+        <c:axId val="431669248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2829,12 +2864,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614385152"/>
+        <c:crossAx val="431670784"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="614385152"/>
+        <c:axId val="431670784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2843,7 +2878,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="614383616"/>
+        <c:crossAx val="431669248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3022,7 +3057,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3190,6 +3225,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3199,7 +3237,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3366,6 +3404,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3409,7 +3450,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3577,6 +3618,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3586,7 +3630,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3754,6 +3798,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>129713726.73870459</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>130068603.42279746</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3796,7 +3843,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3964,6 +4011,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3973,7 +4023,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4141,6 +4191,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>52299020.587816894</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>52653897.271909758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4162,11 +4215,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615924480"/>
-        <c:axId val="615926016"/>
+        <c:axId val="431923968"/>
+        <c:axId val="431925504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615924480"/>
+        <c:axId val="431923968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4209,14 +4262,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615926016"/>
+        <c:crossAx val="431925504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615926016"/>
+        <c:axId val="431925504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4267,7 +4320,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615924480"/>
+        <c:crossAx val="431923968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4458,7 +4511,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4626,6 +4679,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-637497.67999171233</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-313710.67019325693</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4645,8 +4701,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="615954304"/>
-        <c:axId val="615952768"/>
+        <c:axId val="511985536"/>
+        <c:axId val="511984000"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4671,7 +4727,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4839,6 +4895,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4907,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5016,6 +5075,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5037,11 +5099,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="615949440"/>
-        <c:axId val="615950976"/>
+        <c:axId val="511972480"/>
+        <c:axId val="511974016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="615949440"/>
+        <c:axId val="511972480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5084,14 +5146,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615950976"/>
+        <c:crossAx val="511974016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="615950976"/>
+        <c:axId val="511974016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5142,12 +5204,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615949440"/>
+        <c:crossAx val="511972480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="615952768"/>
+        <c:axId val="511984000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5184,12 +5246,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="615954304"/>
+        <c:crossAx val="511985536"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="615954304"/>
+        <c:axId val="511985536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5198,7 +5260,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="615952768"/>
+        <c:crossAx val="511984000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5377,7 +5439,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5545,6 +5607,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5554,7 +5619,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5721,6 +5786,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5764,7 +5832,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5932,6 +6000,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5941,7 +6012,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6109,6 +6180,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>127192525.29663128</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>127535823.14326243</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6151,7 +6225,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6319,6 +6393,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6328,7 +6405,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6496,6 +6573,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45420687.82239458</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>45763985.669025734</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6517,11 +6597,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="616023168"/>
-        <c:axId val="616024704"/>
+        <c:axId val="523416704"/>
+        <c:axId val="523418240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="616023168"/>
+        <c:axId val="523416704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6564,14 +6644,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616024704"/>
+        <c:crossAx val="523418240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="616024704"/>
+        <c:axId val="523418240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6622,7 +6702,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616023168"/>
+        <c:crossAx val="523416704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6813,7 +6893,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6981,6 +7061,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-745710.74747990887</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-660837.59425302898</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7000,8 +7083,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="616511744"/>
-        <c:axId val="616510208"/>
+        <c:axId val="523987200"/>
+        <c:axId val="523985664"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7026,7 +7109,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7194,6 +7277,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7203,7 +7289,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7371,6 +7457,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7392,11 +7481,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="616506880"/>
-        <c:axId val="616508416"/>
+        <c:axId val="523974144"/>
+        <c:axId val="523975680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="616506880"/>
+        <c:axId val="523974144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7439,14 +7528,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616508416"/>
+        <c:crossAx val="523975680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="616508416"/>
+        <c:axId val="523975680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7497,12 +7586,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616506880"/>
+        <c:crossAx val="523974144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="616510208"/>
+        <c:axId val="523985664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7539,12 +7628,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616511744"/>
+        <c:crossAx val="523987200"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="616511744"/>
+        <c:axId val="523987200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7553,7 +7642,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="616510208"/>
+        <c:crossAx val="523985664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7715,7 +7804,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7883,6 +7972,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7902,8 +7994,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="617980288"/>
-        <c:axId val="617978496"/>
+        <c:axId val="546441088"/>
+        <c:axId val="546439552"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7928,7 +8020,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8096,6 +8188,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8105,7 +8200,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8273,6 +8368,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8294,11 +8392,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617974016"/>
-        <c:axId val="617976192"/>
+        <c:axId val="391508352"/>
+        <c:axId val="391509888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617974016"/>
+        <c:axId val="391508352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8341,14 +8439,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617976192"/>
+        <c:crossAx val="391509888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617976192"/>
+        <c:axId val="391509888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8399,12 +8497,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617974016"/>
+        <c:crossAx val="391508352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="617978496"/>
+        <c:axId val="546439552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8441,12 +8539,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617980288"/>
+        <c:crossAx val="546441088"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="617980288"/>
+        <c:axId val="546441088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8455,7 +8553,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="617978496"/>
+        <c:crossAx val="546439552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8634,7 +8732,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8802,6 +8900,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8811,7 +8912,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8978,6 +9079,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9021,7 +9125,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9189,6 +9293,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9198,7 +9305,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9366,6 +9473,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>16482407.681704661</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>16527131.847206756</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9408,7 +9518,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9576,6 +9686,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9585,7 +9698,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9753,6 +9866,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5594571.908223683</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5639296.0737257786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9774,11 +9890,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617994112"/>
-        <c:axId val="617995648"/>
+        <c:axId val="546542720"/>
+        <c:axId val="546544256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617994112"/>
+        <c:axId val="546542720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9821,14 +9937,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617995648"/>
+        <c:crossAx val="546544256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617995648"/>
+        <c:axId val="546544256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9879,7 +9995,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617994112"/>
+        <c:crossAx val="546542720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10091,7 +10207,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10259,6 +10375,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-25998.161012664015</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-23986.056658340185</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10278,8 +10397,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="621659264"/>
-        <c:axId val="621579648"/>
+        <c:axId val="548001664"/>
+        <c:axId val="547999744"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10304,7 +10423,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10472,6 +10591,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10481,7 +10603,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10649,6 +10771,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10670,11 +10795,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="621558784"/>
-        <c:axId val="621576960"/>
+        <c:axId val="547990528"/>
+        <c:axId val="547996800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="621558784"/>
+        <c:axId val="547990528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10717,14 +10842,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621576960"/>
+        <c:crossAx val="547996800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621576960"/>
+        <c:axId val="547996800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10775,12 +10900,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621558784"/>
+        <c:crossAx val="547990528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="621579648"/>
+        <c:axId val="547999744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10817,12 +10942,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621659264"/>
+        <c:crossAx val="548001664"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="621659264"/>
+        <c:axId val="548001664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10831,7 +10956,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="621579648"/>
+        <c:crossAx val="547999744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11010,7 +11135,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11178,6 +11303,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11187,7 +11315,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11354,6 +11482,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11397,7 +11528,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11565,6 +11696,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11574,7 +11708,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11742,6 +11876,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>147929922.55191049</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>148335035.57934332</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11784,7 +11921,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11952,6 +12089,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11961,7 +12101,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12129,6 +12269,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>51781461.723705485</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>52186574.751138315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12150,11 +12293,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="623556864"/>
-        <c:axId val="624558080"/>
+        <c:axId val="548197888"/>
+        <c:axId val="548286464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="623556864"/>
+        <c:axId val="548197888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12197,14 +12340,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="624558080"/>
+        <c:crossAx val="548286464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="624558080"/>
+        <c:axId val="548286464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12255,7 +12398,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623556864"/>
+        <c:crossAx val="548197888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12467,7 +12610,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12635,6 +12778,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-149142.14949598178</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-132167.51885060579</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12654,8 +12800,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="625399680"/>
-        <c:axId val="625398144"/>
+        <c:axId val="548559872"/>
+        <c:axId val="548558336"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12680,7 +12826,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12848,6 +12994,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12857,7 +13006,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13025,6 +13174,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13046,11 +13198,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="625374336"/>
-        <c:axId val="625375872"/>
+        <c:axId val="548485376"/>
+        <c:axId val="548556800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="625374336"/>
+        <c:axId val="548485376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13093,14 +13245,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625375872"/>
+        <c:crossAx val="548556800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="625375872"/>
+        <c:axId val="548556800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13151,12 +13303,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625374336"/>
+        <c:crossAx val="548485376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="625398144"/>
+        <c:axId val="548558336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13193,12 +13345,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625399680"/>
+        <c:crossAx val="548559872"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="625399680"/>
+        <c:axId val="548559872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13207,7 +13359,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="625398144"/>
+        <c:crossAx val="548558336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13386,7 +13538,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13554,6 +13706,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13563,7 +13718,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13730,6 +13885,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -13773,7 +13931,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13941,6 +14099,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13950,7 +14111,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14118,6 +14279,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>20686841.312001664</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>20743984.226547685</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14160,7 +14324,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14328,6 +14492,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14337,7 +14504,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14505,6 +14672,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>8284544.832071906</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>8341687.7466179263</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14526,11 +14696,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="625568768"/>
-        <c:axId val="625570560"/>
+        <c:axId val="617019264"/>
+        <c:axId val="617074048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="625568768"/>
+        <c:axId val="617019264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14573,14 +14743,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625570560"/>
+        <c:crossAx val="617074048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="625570560"/>
+        <c:axId val="617074048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14631,7 +14801,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625568768"/>
+        <c:crossAx val="617019264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14822,7 +14992,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14990,6 +15160,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-17753.099949136293</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-8736.2465117109532</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15009,8 +15182,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="625970560"/>
-        <c:axId val="625969024"/>
+        <c:axId val="623246720"/>
+        <c:axId val="623244800"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15035,7 +15208,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15203,6 +15376,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15212,7 +15388,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15380,6 +15556,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1.0720000267028809</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.0750000476837158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15401,11 +15580,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="625846528"/>
-        <c:axId val="625967104"/>
+        <c:axId val="620451328"/>
+        <c:axId val="620453248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="625846528"/>
+        <c:axId val="620451328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15448,14 +15627,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625967104"/>
+        <c:crossAx val="620453248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="625967104"/>
+        <c:axId val="620453248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15506,12 +15685,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625846528"/>
+        <c:crossAx val="620451328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="625969024"/>
+        <c:axId val="623244800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15548,12 +15727,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="625970560"/>
+        <c:crossAx val="623246720"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="625970560"/>
+        <c:axId val="623246720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15562,7 +15741,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="625969024"/>
+        <c:crossAx val="623244800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15741,7 +15920,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15909,6 +16088,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15918,7 +16100,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16085,6 +16267,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -16128,7 +16313,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16296,6 +16481,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16305,7 +16493,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16473,6 +16661,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>14626457.465711212</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14665268.017369246</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16515,7 +16706,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16683,6 +16874,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16692,7 +16886,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16860,6 +17054,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>5092387.8871402442</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5131198.4387982786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16881,11 +17078,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="568107392"/>
-        <c:axId val="568108928"/>
+        <c:axId val="389128576"/>
+        <c:axId val="389130112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="568107392"/>
+        <c:axId val="389128576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16928,14 +17125,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568108928"/>
+        <c:crossAx val="389130112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="568108928"/>
+        <c:axId val="389130112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16986,7 +17183,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="568107392"/>
+        <c:crossAx val="389128576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17922,7 +18119,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18053,28 +18250,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>15</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20411,6 +20608,44 @@
       </c>
       <c r="L58" s="29">
         <v>758250.31664433924</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="32">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="31">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="29">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="29">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="30">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="30">
+        <v>12548379.99314902</v>
+      </c>
+      <c r="H59" s="30">
+        <v>13489509.090988582</v>
+      </c>
+      <c r="I59" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J59" s="30">
+        <v>14367689.690924622</v>
+      </c>
+      <c r="K59" s="30">
+        <v>5006354.8731971979</v>
+      </c>
+      <c r="L59" s="29">
+        <v>878180.59993604012</v>
       </c>
     </row>
   </sheetData>
@@ -20429,7 +20664,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20464,16 +20699,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -20571,13 +20806,13 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
@@ -20589,10 +20824,10 @@
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23570,6 +23805,56 @@
         <v>78.476878875019352</v>
       </c>
       <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-23986.056658340185</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-22312.609855248407</v>
+      </c>
+      <c r="G59" s="18">
+        <v>14885638.297090929</v>
+      </c>
+      <c r="H59" s="18">
+        <v>16002061.879175294</v>
+      </c>
+      <c r="I59" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J59" s="18">
+        <v>16527131.847206756</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5639296.0737257786</v>
+      </c>
+      <c r="L59" s="17">
+        <v>525069.96803146251</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23589,7 +23874,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH58"/>
+  <dimension ref="A1:AH59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23624,16 +23909,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23660,7 +23945,7 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>23</v>
@@ -23731,13 +24016,13 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
@@ -23749,10 +24034,10 @@
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -26730,6 +27015,56 @@
         <v>78.476878875019352</v>
       </c>
       <c r="P58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-132167.51885060579</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-122946.52370982204</v>
+      </c>
+      <c r="G59" s="18">
+        <v>134913784.89278081</v>
+      </c>
+      <c r="H59" s="18">
+        <v>145032325.19292995</v>
+      </c>
+      <c r="I59" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J59" s="18">
+        <v>148335035.57934332</v>
+      </c>
+      <c r="K59" s="18">
+        <v>52186574.751138315</v>
+      </c>
+      <c r="L59" s="17">
+        <v>3302710.386413367</v>
+      </c>
+      <c r="M59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="N59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="O59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="P59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -26749,7 +27084,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -26784,22 +27119,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -26826,7 +27161,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="P1" s="44" t="s">
         <v>23</v>
@@ -26909,13 +27244,13 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
@@ -26927,10 +27262,10 @@
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30238,6 +30573,62 @@
         <v>78.476878875019352</v>
       </c>
       <c r="R58" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-8736.2465117109532</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-8126.7405806490833</v>
+      </c>
+      <c r="I59" s="18">
+        <v>19039378.230574112</v>
+      </c>
+      <c r="J59" s="18">
+        <v>20467332.505735472</v>
+      </c>
+      <c r="K59" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L59" s="18">
+        <v>20743984.226547685</v>
+      </c>
+      <c r="M59" s="18">
+        <v>8341687.7466179263</v>
+      </c>
+      <c r="N59" s="17">
+        <v>276651.72081221337</v>
+      </c>
+      <c r="O59" s="22">
+        <v>2.4512387592351127E-2</v>
+      </c>
+      <c r="P59" s="22">
+        <v>3.1098040064731682E-2</v>
+      </c>
+      <c r="Q59" s="22">
+        <v>78.82293398981966</v>
+      </c>
+      <c r="R59" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -30257,7 +30648,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30292,16 +30683,16 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -30328,19 +30719,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30418,13 +30809,13 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
@@ -30436,10 +30827,10 @@
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -33585,6 +33976,59 @@
         <v>80.679300446476333</v>
       </c>
       <c r="Q58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-111563.04927624203</v>
+      </c>
+      <c r="G59" s="18">
+        <v>12825197.028725727</v>
+      </c>
+      <c r="H59" s="18">
+        <v>13787087.417433206</v>
+      </c>
+      <c r="I59" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J59" s="18">
+        <v>14665268.017369246</v>
+      </c>
+      <c r="K59" s="18">
+        <v>5131198.4387982786</v>
+      </c>
+      <c r="L59" s="17">
+        <v>878180.59993604012</v>
+      </c>
+      <c r="M59" s="21">
+        <v>79.947236522705992</v>
+      </c>
+      <c r="N59" s="21">
+        <v>80.74151427845328</v>
+      </c>
+      <c r="O59" s="21">
+        <v>81.15939110031924</v>
+      </c>
+      <c r="P59" s="21">
+        <v>79.905760634721361</v>
+      </c>
+      <c r="Q59" s="1">
         <v>1</v>
       </c>
     </row>
@@ -33604,7 +34048,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ58"/>
+  <dimension ref="A1:AJ59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -33639,22 +34083,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -33750,13 +34194,13 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
@@ -33768,10 +34212,10 @@
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36438,6 +36882,50 @@
       </c>
       <c r="N58" s="17">
         <v>2905341.9793752134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>1968100</v>
+      </c>
+      <c r="F59" s="17">
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="G59" s="17">
+        <v>-313710.67019325693</v>
+      </c>
+      <c r="H59" s="18">
+        <v>-291823.86630512617</v>
+      </c>
+      <c r="I59" s="18">
+        <v>117999576.88053088</v>
+      </c>
+      <c r="J59" s="18">
+        <v>126849550.77322899</v>
+      </c>
+      <c r="K59" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L59" s="18">
+        <v>130068603.42279746</v>
+      </c>
+      <c r="M59" s="18">
+        <v>52653897.271909758</v>
+      </c>
+      <c r="N59" s="17">
+        <v>3219052.6495684702</v>
       </c>
     </row>
   </sheetData>
@@ -36456,7 +36944,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36491,16 +36979,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -36587,13 +37075,13 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
@@ -36605,10 +37093,10 @@
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -38945,6 +39433,44 @@
       </c>
       <c r="L58" s="17">
         <v>4521616.2907800153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B59" s="31">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C59" s="16">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D59" s="17">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E59" s="17">
+        <v>-660837.59425302898</v>
+      </c>
+      <c r="F59" s="18">
+        <v>-614732.61854911025</v>
+      </c>
+      <c r="G59" s="18">
+        <v>113817082.63349578</v>
+      </c>
+      <c r="H59" s="18">
+        <v>122353369.25822939</v>
+      </c>
+      <c r="I59" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J59" s="18">
+        <v>127535823.14326243</v>
+      </c>
+      <c r="K59" s="18">
+        <v>45763985.669025734</v>
+      </c>
+      <c r="L59" s="17">
+        <v>5182453.885033044</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="29">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -133,15 +133,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>总资产</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>盈利金额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>回收资金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -150,14 +142,6 @@
   </si>
   <si>
     <t>年化收益率</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -174,18 +158,6 @@
   </si>
   <si>
     <t>标志</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>深创100ETF</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE均值</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -614,7 +586,7 @@
               </a:rPr>
               <a:t>）</a:t>
             </a:r>
-            <a:endParaRPr/>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -675,7 +647,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -846,6 +818,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -855,7 +830,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1025,6 +1000,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1068,7 +1046,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1239,6 +1217,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1248,7 +1229,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1419,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14367689.690924622</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14028882.557513656</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1461,7 +1445,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1632,6 +1616,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1641,7 +1628,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1812,6 +1799,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5006354.8731971979</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4667547.7397862319</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1833,11 +1823,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="391471488"/>
-        <c:axId val="391473408"/>
+        <c:axId val="527218560"/>
+        <c:axId val="527224832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="391471488"/>
+        <c:axId val="527218560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1880,14 +1870,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391473408"/>
+        <c:crossAx val="527224832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="391473408"/>
+        <c:axId val="527224832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1938,7 +1928,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391471488"/>
+        <c:crossAx val="527218560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2129,7 +2119,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2300,6 +2290,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2319,8 +2312,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="431670784"/>
-        <c:axId val="431669248"/>
+        <c:axId val="526468992"/>
+        <c:axId val="526467456"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2345,7 +2338,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2516,6 +2509,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2525,7 +2521,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2696,6 +2692,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2717,11 +2716,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="392872704"/>
-        <c:axId val="392874240"/>
+        <c:axId val="526460032"/>
+        <c:axId val="526461568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="392872704"/>
+        <c:axId val="526460032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2764,14 +2763,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392874240"/>
+        <c:crossAx val="526461568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="392874240"/>
+        <c:axId val="526461568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2822,12 +2821,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="392872704"/>
+        <c:crossAx val="526460032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="431669248"/>
+        <c:axId val="526467456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2864,12 +2863,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431670784"/>
+        <c:crossAx val="526468992"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="431670784"/>
+        <c:axId val="526468992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2878,7 +2877,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="431669248"/>
+        <c:crossAx val="526467456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3057,7 +3056,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3228,6 +3227,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3237,7 +3239,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3407,6 +3409,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3450,7 +3455,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3621,6 +3626,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3630,7 +3638,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3801,6 +3809,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>130068603.42279746</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>126882606.63210201</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3843,7 +3854,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4014,6 +4025,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4023,7 +4037,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4194,6 +4208,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>52653897.271909758</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>49467900.481214315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4215,11 +4232,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="431923968"/>
-        <c:axId val="431925504"/>
+        <c:axId val="526484608"/>
+        <c:axId val="526486144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="431923968"/>
+        <c:axId val="526484608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4262,14 +4279,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431925504"/>
+        <c:crossAx val="526486144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="431925504"/>
+        <c:axId val="526486144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4320,7 +4337,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="431923968"/>
+        <c:crossAx val="526484608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4511,7 +4528,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4682,6 +4699,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-313710.67019325693</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-166564.10795343228</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4701,8 +4721,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="511985536"/>
-        <c:axId val="511984000"/>
+        <c:axId val="527173888"/>
+        <c:axId val="527172352"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4727,7 +4747,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4898,6 +4918,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4907,7 +4930,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5078,6 +5101,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5099,11 +5125,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511972480"/>
-        <c:axId val="511974016"/>
+        <c:axId val="527099392"/>
+        <c:axId val="527100928"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511972480"/>
+        <c:axId val="527099392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5146,14 +5172,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511974016"/>
+        <c:crossAx val="527100928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511974016"/>
+        <c:axId val="527100928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5204,12 +5230,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511972480"/>
+        <c:crossAx val="527099392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="511984000"/>
+        <c:axId val="527172352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5246,12 +5272,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511985536"/>
+        <c:crossAx val="527173888"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="511985536"/>
+        <c:axId val="527173888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5260,7 +5286,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="511984000"/>
+        <c:crossAx val="527172352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5439,7 +5465,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5610,6 +5636,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5619,7 +5648,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5789,6 +5818,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5832,7 +5864,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6003,6 +6035,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6012,7 +6047,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6183,6 +6218,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>127535823.14326243</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>124462753.98841476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,7 +6263,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6396,6 +6434,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6405,7 +6446,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6576,6 +6617,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>45763985.669025734</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>42690916.514178067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6597,11 +6641,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523416704"/>
-        <c:axId val="523418240"/>
+        <c:axId val="528508416"/>
+        <c:axId val="528509952"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523416704"/>
+        <c:axId val="528508416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6644,14 +6688,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523418240"/>
+        <c:crossAx val="528509952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523418240"/>
+        <c:axId val="528509952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6702,7 +6746,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523416704"/>
+        <c:crossAx val="528508416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6893,7 +6937,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7064,6 +7108,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-660837.59425302898</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-339472.02214159875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7083,8 +7130,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="523987200"/>
-        <c:axId val="523985664"/>
+        <c:axId val="529152640"/>
+        <c:axId val="529151104"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7109,7 +7156,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7280,6 +7327,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7289,7 +7339,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7460,6 +7510,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7481,11 +7534,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523974144"/>
-        <c:axId val="523975680"/>
+        <c:axId val="529106816"/>
+        <c:axId val="529108352"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523974144"/>
+        <c:axId val="529106816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7528,14 +7581,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523975680"/>
+        <c:crossAx val="529108352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523975680"/>
+        <c:axId val="529108352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7586,12 +7639,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523974144"/>
+        <c:crossAx val="529106816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="523985664"/>
+        <c:axId val="529151104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7628,12 +7681,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523987200"/>
+        <c:crossAx val="529152640"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="523987200"/>
+        <c:axId val="529152640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7642,7 +7695,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="523985664"/>
+        <c:crossAx val="529151104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7804,7 +7857,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7975,6 +8028,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7994,8 +8050,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="546441088"/>
-        <c:axId val="546439552"/>
+        <c:axId val="533336832"/>
+        <c:axId val="533335040"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8020,7 +8076,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8191,6 +8247,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8200,7 +8259,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8371,6 +8430,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8392,11 +8454,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="391508352"/>
-        <c:axId val="391509888"/>
+        <c:axId val="533328256"/>
+        <c:axId val="533333504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="391508352"/>
+        <c:axId val="533328256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8439,14 +8501,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391509888"/>
+        <c:crossAx val="533333504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="391509888"/>
+        <c:axId val="533333504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8497,12 +8559,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="391508352"/>
+        <c:crossAx val="533328256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="546439552"/>
+        <c:axId val="533335040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8539,12 +8601,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546441088"/>
+        <c:crossAx val="533336832"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="546441088"/>
+        <c:axId val="533336832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8553,7 +8615,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="546439552"/>
+        <c:crossAx val="533335040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8732,7 +8794,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8903,6 +8965,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8912,7 +8977,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9082,6 +9147,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9125,7 +9193,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9296,6 +9364,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9305,7 +9376,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9476,6 +9547,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>16527131.847206756</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>16125218.576873584</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9518,7 +9592,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9689,6 +9763,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9698,7 +9775,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9869,6 +9946,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5639296.0737257786</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5237382.8033926059</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9890,11 +9970,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="546542720"/>
-        <c:axId val="546544256"/>
+        <c:axId val="533363328"/>
+        <c:axId val="533370752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="546542720"/>
+        <c:axId val="533363328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9937,14 +10017,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546544256"/>
+        <c:crossAx val="533370752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546544256"/>
+        <c:axId val="533370752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9995,7 +10075,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546542720"/>
+        <c:crossAx val="533363328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10207,7 +10287,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10378,6 +10458,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-23986.056658340185</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-15385.030177591741</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10397,8 +10480,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="548001664"/>
-        <c:axId val="547999744"/>
+        <c:axId val="538071040"/>
+        <c:axId val="538064384"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10423,7 +10506,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10594,6 +10677,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10603,7 +10689,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10774,6 +10860,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10795,11 +10884,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547990528"/>
-        <c:axId val="547996800"/>
+        <c:axId val="537819392"/>
+        <c:axId val="538062848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547990528"/>
+        <c:axId val="537819392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10842,14 +10931,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547996800"/>
+        <c:crossAx val="538062848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547996800"/>
+        <c:axId val="538062848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10900,12 +10989,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547990528"/>
+        <c:crossAx val="537819392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="547999744"/>
+        <c:axId val="538064384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10942,12 +11031,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548001664"/>
+        <c:crossAx val="538071040"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="548001664"/>
+        <c:axId val="538071040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10956,7 +11045,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="547999744"/>
+        <c:crossAx val="538064384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11135,7 +11224,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11306,6 +11395,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11315,7 +11407,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11485,6 +11577,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11528,7 +11623,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11699,6 +11794,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11708,7 +11806,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11879,6 +11977,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>148335035.57934332</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>144692353.99478</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11921,7 +12022,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12092,6 +12193,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12101,7 +12205,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12272,6 +12376,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>52186574.751138315</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>48543893.166575</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12293,11 +12400,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548197888"/>
-        <c:axId val="548286464"/>
+        <c:axId val="538317568"/>
+        <c:axId val="538319872"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548197888"/>
+        <c:axId val="538317568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12340,14 +12447,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548286464"/>
+        <c:crossAx val="538319872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548286464"/>
+        <c:axId val="538319872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12398,7 +12505,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548197888"/>
+        <c:crossAx val="538317568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12610,7 +12717,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12781,6 +12888,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-132167.51885060579</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-67894.404428319758</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12800,8 +12910,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="548559872"/>
-        <c:axId val="548558336"/>
+        <c:axId val="540056192"/>
+        <c:axId val="540054656"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12826,7 +12936,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12997,6 +13107,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13006,7 +13119,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13177,6 +13290,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13198,11 +13314,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="548485376"/>
-        <c:axId val="548556800"/>
+        <c:axId val="540041984"/>
+        <c:axId val="540043904"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="548485376"/>
+        <c:axId val="540041984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13245,14 +13361,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548556800"/>
+        <c:crossAx val="540043904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="548556800"/>
+        <c:axId val="540043904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13303,12 +13419,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548485376"/>
+        <c:crossAx val="540041984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="548558336"/>
+        <c:axId val="540054656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13345,12 +13461,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="548559872"/>
+        <c:crossAx val="540056192"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="548559872"/>
+        <c:axId val="540056192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13359,7 +13475,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="548558336"/>
+        <c:crossAx val="540054656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13538,7 +13654,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13709,6 +13825,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13718,7 +13837,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13888,6 +14007,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -13931,7 +14053,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14102,6 +14224,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14111,7 +14236,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14282,6 +14407,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>20743984.226547685</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>20229919.688834462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14324,7 +14452,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14495,6 +14623,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14504,7 +14635,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14675,6 +14806,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>8341687.7466179263</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7827623.2089047041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14696,11 +14830,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617019264"/>
-        <c:axId val="617074048"/>
+        <c:axId val="566652928"/>
+        <c:axId val="566654848"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617019264"/>
+        <c:axId val="566652928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14743,14 +14877,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617074048"/>
+        <c:crossAx val="566654848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617074048"/>
+        <c:axId val="566654848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14801,7 +14935,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617019264"/>
+        <c:crossAx val="566652928"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14992,7 +15126,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15163,6 +15297,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-8736.2465117109532</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-4638.4941455386206</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15182,8 +15319,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="623246720"/>
-        <c:axId val="623244800"/>
+        <c:axId val="429753856"/>
+        <c:axId val="429752320"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15208,7 +15345,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15379,6 +15516,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15388,7 +15528,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15559,6 +15699,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1.0750000476837158</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.0479999780654907</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15580,11 +15723,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="620451328"/>
-        <c:axId val="620453248"/>
+        <c:axId val="429744896"/>
+        <c:axId val="429746432"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="620451328"/>
+        <c:axId val="429744896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15627,14 +15770,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620453248"/>
+        <c:crossAx val="429746432"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="620453248"/>
+        <c:axId val="429746432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15685,12 +15828,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620451328"/>
+        <c:crossAx val="429744896"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="623244800"/>
+        <c:axId val="429752320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15727,12 +15870,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623246720"/>
+        <c:crossAx val="429753856"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="623246720"/>
+        <c:axId val="429753856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15741,7 +15884,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="623244800"/>
+        <c:crossAx val="429752320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -15920,7 +16063,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16091,6 +16234,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16100,7 +16246,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16270,6 +16416,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -16313,7 +16462,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16484,6 +16633,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16493,7 +16645,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16664,6 +16816,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14665268.017369246</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14318986.804726198</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16706,7 +16861,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16877,6 +17032,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16886,7 +17044,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17057,6 +17215,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5131198.4387982786</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4784917.2261552308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17078,11 +17239,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="389128576"/>
-        <c:axId val="389130112"/>
+        <c:axId val="433320704"/>
+        <c:axId val="433322240"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="389128576"/>
+        <c:axId val="433320704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17125,14 +17286,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389130112"/>
+        <c:crossAx val="433322240"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="389130112"/>
+        <c:axId val="433322240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17183,7 +17344,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="389128576"/>
+        <c:crossAx val="433320704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18119,7 +18280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18259,19 +18420,19 @@
         <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="47" t="s">
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="V3" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>19</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20646,6 +20807,44 @@
       </c>
       <c r="L59" s="29">
         <v>878180.59993604012</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="32">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="31">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="29">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="29">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="30">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="30">
+        <v>12474978.130078416</v>
+      </c>
+      <c r="H60" s="30">
+        <v>13073776.806689657</v>
+      </c>
+      <c r="I60" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J60" s="30">
+        <v>14028882.557513656</v>
+      </c>
+      <c r="K60" s="30">
+        <v>4667547.7397862319</v>
+      </c>
+      <c r="L60" s="29">
+        <v>955105.75082399882</v>
       </c>
     </row>
   </sheetData>
@@ -20664,7 +20863,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20699,10 +20898,10 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -20735,16 +20934,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -20818,16 +21017,16 @@
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -23855,6 +24054,56 @@
         <v>78.82293398981966</v>
       </c>
       <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-15385.030177591741</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-14680.372614120717</v>
+      </c>
+      <c r="G60" s="18">
+        <v>14870957.924476808</v>
+      </c>
+      <c r="H60" s="18">
+        <v>15584763.57866453</v>
+      </c>
+      <c r="I60" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J60" s="18">
+        <v>16125218.576873584</v>
+      </c>
+      <c r="K60" s="18">
+        <v>5237382.8033926059</v>
+      </c>
+      <c r="L60" s="17">
+        <v>540454.99820905423</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -23874,7 +24123,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -23909,16 +24158,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -23945,16 +24194,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24028,16 +24277,16 @@
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27065,6 +27314,56 @@
         <v>78.82293398981966</v>
       </c>
       <c r="P59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-67894.404428319758</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-64784.738405859927</v>
+      </c>
+      <c r="G60" s="18">
+        <v>134849000.15437496</v>
+      </c>
+      <c r="H60" s="18">
+        <v>141321749.20393831</v>
+      </c>
+      <c r="I60" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J60" s="18">
+        <v>144692353.99478</v>
+      </c>
+      <c r="K60" s="18">
+        <v>48543893.166575</v>
+      </c>
+      <c r="L60" s="17">
+        <v>3370604.7908416865</v>
+      </c>
+      <c r="M60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="N60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="O60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="P60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -27084,7 +27383,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27131,10 +27430,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27161,16 +27460,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -27256,16 +27555,16 @@
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30629,6 +30928,62 @@
         <v>78.82293398981966</v>
       </c>
       <c r="R59" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-4638.4941455386206</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-4426.0441246390519</v>
+      </c>
+      <c r="I60" s="18">
+        <v>19034952.186449472</v>
+      </c>
+      <c r="J60" s="18">
+        <v>19948629.473876711</v>
+      </c>
+      <c r="K60" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L60" s="18">
+        <v>20229919.688834462</v>
+      </c>
+      <c r="M60" s="18">
+        <v>7827623.2089047041</v>
+      </c>
+      <c r="N60" s="17">
+        <v>281290.21495775197</v>
+      </c>
+      <c r="O60" s="22">
+        <v>2.0426989660292605E-2</v>
+      </c>
+      <c r="P60" s="22">
+        <v>3.0415044990313916E-2</v>
+      </c>
+      <c r="Q60" s="22">
+        <v>67.160806984825626</v>
+      </c>
+      <c r="R60" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -30648,7 +31003,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -30719,19 +31074,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -30821,16 +31176,16 @@
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34029,6 +34384,59 @@
         <v>79.905760634721361</v>
       </c>
       <c r="Q59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-73401.863070603576</v>
+      </c>
+      <c r="G60" s="18">
+        <v>12751795.165655123</v>
+      </c>
+      <c r="H60" s="18">
+        <v>13363881.053902199</v>
+      </c>
+      <c r="I60" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J60" s="18">
+        <v>14318986.804726198</v>
+      </c>
+      <c r="K60" s="18">
+        <v>4784917.2261552308</v>
+      </c>
+      <c r="L60" s="17">
+        <v>955105.75082399882</v>
+      </c>
+      <c r="M60" s="21">
+        <v>70.655258802170835</v>
+      </c>
+      <c r="N60" s="21">
+        <v>77.37942911969246</v>
+      </c>
+      <c r="O60" s="21">
+        <v>79.899403773443638</v>
+      </c>
+      <c r="P60" s="21">
+        <v>72.339479812190092</v>
+      </c>
+      <c r="Q60" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34048,7 +34456,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ59"/>
+  <dimension ref="A1:AJ60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34095,10 +34503,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -34206,16 +34614,16 @@
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -36926,6 +37334,50 @@
       </c>
       <c r="N59" s="17">
         <v>3219052.6495684702</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2017527</v>
+      </c>
+      <c r="F60" s="17">
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="G60" s="17">
+        <v>-166564.10795343228</v>
+      </c>
+      <c r="H60" s="18">
+        <v>-158935.2208393114</v>
+      </c>
+      <c r="I60" s="18">
+        <v>117840641.65969157</v>
+      </c>
+      <c r="J60" s="18">
+        <v>123496989.87458012</v>
+      </c>
+      <c r="K60" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L60" s="18">
+        <v>126882606.63210201</v>
+      </c>
+      <c r="M60" s="18">
+        <v>49467900.481214315</v>
+      </c>
+      <c r="N60" s="17">
+        <v>3385616.7575219027</v>
       </c>
     </row>
   </sheetData>
@@ -36944,7 +37396,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -36979,10 +37431,10 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -37087,16 +37539,16 @@
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -39471,6 +39923,44 @@
       </c>
       <c r="L59" s="17">
         <v>5182453.885033044</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B60" s="31">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="C60" s="16">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D60" s="17">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E60" s="17">
+        <v>-339472.02214159875</v>
+      </c>
+      <c r="F60" s="18">
+        <v>-323923.69202929962</v>
+      </c>
+      <c r="G60" s="18">
+        <v>113493158.94146648</v>
+      </c>
+      <c r="H60" s="18">
+        <v>118940828.08124012</v>
+      </c>
+      <c r="I60" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J60" s="18">
+        <v>124462753.98841476</v>
+      </c>
+      <c r="K60" s="18">
+        <v>42690916.514178067</v>
+      </c>
+      <c r="L60" s="17">
+        <v>5521925.9071746431</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,6 +125,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -145,6 +149,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>深创100ETF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE均值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SMA之MAX</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -158,6 +174,10 @@
   </si>
   <si>
     <t>标志</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -647,7 +667,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -821,6 +841,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -830,7 +853,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1003,6 +1026,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1046,7 +1072,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1220,6 +1246,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1229,7 +1258,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1403,6 +1432,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14028882.557513656</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15638155.580985475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1445,7 +1477,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1619,6 +1651,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1628,7 +1663,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1802,6 +1837,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4667547.7397862319</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6276820.7632580511</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1823,11 +1861,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527218560"/>
-        <c:axId val="527224832"/>
+        <c:axId val="444378112"/>
+        <c:axId val="444380288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527218560"/>
+        <c:axId val="444378112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1870,14 +1908,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527224832"/>
+        <c:crossAx val="444380288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527224832"/>
+        <c:axId val="444380288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1928,7 +1966,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527218560"/>
+        <c:crossAx val="444378112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2119,7 +2157,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2293,6 +2331,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2312,8 +2353,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="526468992"/>
-        <c:axId val="526467456"/>
+        <c:axId val="467548800"/>
+        <c:axId val="467547264"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2338,7 +2379,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2512,6 +2553,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2521,7 +2565,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2695,6 +2739,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2716,11 +2763,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526460032"/>
-        <c:axId val="526461568"/>
+        <c:axId val="467543936"/>
+        <c:axId val="467545472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526460032"/>
+        <c:axId val="467543936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2763,14 +2810,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526461568"/>
+        <c:crossAx val="467545472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526461568"/>
+        <c:axId val="467545472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,12 +2868,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526460032"/>
+        <c:crossAx val="467543936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="526467456"/>
+        <c:axId val="467547264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2863,12 +2910,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526468992"/>
+        <c:crossAx val="467548800"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="526468992"/>
+        <c:axId val="467548800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2877,7 +2924,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="526467456"/>
+        <c:crossAx val="467547264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3056,7 +3103,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3230,6 +3277,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3239,7 +3289,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3412,6 +3462,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3455,7 +3508,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3629,6 +3682,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3638,7 +3694,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3812,6 +3868,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>126882606.63210201</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>142084057.38529536</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3854,7 +3913,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4028,6 +4087,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4037,7 +4099,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4211,6 +4273,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>49467900.481214315</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>64669351.234407663</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4232,11 +4297,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="526484608"/>
-        <c:axId val="526486144"/>
+        <c:axId val="487425920"/>
+        <c:axId val="487427456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="526484608"/>
+        <c:axId val="487425920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4279,14 +4344,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526486144"/>
+        <c:crossAx val="487427456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526486144"/>
+        <c:axId val="487427456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4337,7 +4402,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526484608"/>
+        <c:crossAx val="487425920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4528,7 +4593,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4702,6 +4767,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-166564.10795343228</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-848400.08660027001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4721,8 +4789,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="527173888"/>
-        <c:axId val="527172352"/>
+        <c:axId val="487455744"/>
+        <c:axId val="487454208"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4747,7 +4815,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4921,6 +4989,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4930,7 +5001,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5104,6 +5175,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5125,11 +5199,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527099392"/>
-        <c:axId val="527100928"/>
+        <c:axId val="487450880"/>
+        <c:axId val="487452672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527099392"/>
+        <c:axId val="487450880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5172,14 +5246,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527100928"/>
+        <c:crossAx val="487452672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527100928"/>
+        <c:axId val="487452672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5230,12 +5304,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527099392"/>
+        <c:crossAx val="487450880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="527172352"/>
+        <c:axId val="487454208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5272,12 +5346,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527173888"/>
+        <c:crossAx val="487455744"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="527173888"/>
+        <c:axId val="487455744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5286,7 +5360,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="527172352"/>
+        <c:crossAx val="487454208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5465,7 +5539,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5639,6 +5713,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5648,7 +5725,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5821,6 +5898,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5864,7 +5944,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6038,6 +6118,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6047,7 +6130,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6221,6 +6304,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>124462753.98841476</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>139103379.1765852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6263,7 +6349,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6437,6 +6523,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6446,7 +6535,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6620,6 +6709,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>42690916.514178067</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>57331541.7023485</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6641,11 +6733,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528508416"/>
-        <c:axId val="528509952"/>
+        <c:axId val="489319040"/>
+        <c:axId val="489333120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528508416"/>
+        <c:axId val="489319040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6688,14 +6780,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528509952"/>
+        <c:crossAx val="489333120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528509952"/>
+        <c:axId val="489333120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6746,7 +6838,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528508416"/>
+        <c:crossAx val="489319040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6937,7 +7029,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7111,6 +7203,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-339472.02214159875</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-2256476.8381611248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7130,8 +7225,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529152640"/>
-        <c:axId val="529151104"/>
+        <c:axId val="529940480"/>
+        <c:axId val="489355520"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7156,7 +7251,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7330,6 +7425,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7339,7 +7437,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7513,6 +7611,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7534,11 +7635,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="529106816"/>
-        <c:axId val="529108352"/>
+        <c:axId val="489352192"/>
+        <c:axId val="489353984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="529106816"/>
+        <c:axId val="489352192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7581,14 +7682,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529108352"/>
+        <c:crossAx val="489353984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="529108352"/>
+        <c:axId val="489353984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7639,12 +7740,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529106816"/>
+        <c:crossAx val="489352192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529151104"/>
+        <c:axId val="489355520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7681,12 +7782,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529152640"/>
+        <c:crossAx val="529940480"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529152640"/>
+        <c:axId val="529940480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7695,7 +7796,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529151104"/>
+        <c:crossAx val="489355520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7857,7 +7958,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8031,6 +8132,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8050,8 +8154,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="533336832"/>
-        <c:axId val="533335040"/>
+        <c:axId val="572200448"/>
+        <c:axId val="572197888"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8076,7 +8180,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8250,6 +8354,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8259,7 +8366,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8433,6 +8540,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8454,11 +8564,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="533328256"/>
-        <c:axId val="533333504"/>
+        <c:axId val="562884992"/>
+        <c:axId val="562886528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533328256"/>
+        <c:axId val="562884992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8501,14 +8611,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533333504"/>
+        <c:crossAx val="562886528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533333504"/>
+        <c:axId val="562886528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8559,12 +8669,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533328256"/>
+        <c:crossAx val="562884992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="533335040"/>
+        <c:axId val="572197888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8601,12 +8711,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533336832"/>
+        <c:crossAx val="572200448"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="533336832"/>
+        <c:axId val="572200448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8615,7 +8725,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="533335040"/>
+        <c:crossAx val="572197888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8794,7 +8904,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8968,6 +9078,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8977,7 +9090,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9150,6 +9263,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9193,7 +9309,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9367,6 +9483,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9376,7 +9495,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9550,6 +9669,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>16125218.576873584</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>18043573.156056687</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9592,7 +9714,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9766,6 +9888,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9775,7 +9900,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9949,6 +10074,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5237382.8033926059</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7155737.3825757094</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9970,11 +10098,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="533363328"/>
-        <c:axId val="533370752"/>
+        <c:axId val="572288384"/>
+        <c:axId val="572298368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533363328"/>
+        <c:axId val="572288384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10017,14 +10145,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533370752"/>
+        <c:crossAx val="572298368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533370752"/>
+        <c:axId val="572298368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10075,7 +10203,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533363328"/>
+        <c:crossAx val="572288384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10287,7 +10415,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10461,6 +10589,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-15385.030177591741</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-54389.65209982227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10480,8 +10611,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="538071040"/>
-        <c:axId val="538064384"/>
+        <c:axId val="573272832"/>
+        <c:axId val="573250176"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10506,7 +10637,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10680,6 +10811,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10689,7 +10823,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -10863,6 +10997,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10884,11 +11021,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="537819392"/>
-        <c:axId val="538062848"/>
+        <c:axId val="573233408"/>
+        <c:axId val="573247488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="537819392"/>
+        <c:axId val="573233408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10931,14 +11068,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538062848"/>
+        <c:crossAx val="573247488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538062848"/>
+        <c:axId val="573247488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10989,12 +11126,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="537819392"/>
+        <c:crossAx val="573233408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="538064384"/>
+        <c:axId val="573250176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11031,12 +11168,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538071040"/>
+        <c:crossAx val="573272832"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="538071040"/>
+        <c:axId val="573272832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11045,7 +11182,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="538064384"/>
+        <c:crossAx val="573250176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11224,7 +11361,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11398,6 +11535,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11407,7 +11547,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11580,6 +11720,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11623,7 +11766,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11797,6 +11940,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11806,7 +11952,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11980,6 +12126,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>144692353.99478</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>162087884.14543834</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12022,7 +12171,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12196,6 +12345,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12205,7 +12357,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12379,6 +12531,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>48543893.166575</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>65939423.317233339</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12400,11 +12555,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538317568"/>
-        <c:axId val="538319872"/>
+        <c:axId val="573526784"/>
+        <c:axId val="573528320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538317568"/>
+        <c:axId val="573526784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12447,14 +12602,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538319872"/>
+        <c:crossAx val="573528320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="538319872"/>
+        <c:axId val="573528320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12505,7 +12660,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538317568"/>
+        <c:crossAx val="573526784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12717,7 +12872,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12891,6 +13046,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-67894.404428319758</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-451295.36763222498</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12910,8 +13068,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="540056192"/>
-        <c:axId val="540054656"/>
+        <c:axId val="573789312"/>
+        <c:axId val="573676928"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -12936,7 +13094,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13110,6 +13268,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13119,7 +13280,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13293,6 +13454,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13314,11 +13478,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="540041984"/>
-        <c:axId val="540043904"/>
+        <c:axId val="573673472"/>
+        <c:axId val="573675392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="540041984"/>
+        <c:axId val="573673472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13361,14 +13525,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540043904"/>
+        <c:crossAx val="573675392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="540043904"/>
+        <c:axId val="573675392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13419,12 +13583,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540041984"/>
+        <c:crossAx val="573673472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="540054656"/>
+        <c:axId val="573676928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13461,12 +13625,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="540056192"/>
+        <c:crossAx val="573789312"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="540056192"/>
+        <c:axId val="573789312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13475,7 +13639,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="540054656"/>
+        <c:crossAx val="573676928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13654,7 +13818,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13828,6 +13992,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13837,7 +14004,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14010,6 +14177,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -14053,7 +14223,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14227,6 +14397,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14236,7 +14409,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14410,6 +14583,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>20229919.688834462</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>22685429.809759744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14452,7 +14628,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14626,6 +14802,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14635,7 +14814,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14809,6 +14988,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>7827623.2089047041</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>10283133.329829985</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14830,11 +15012,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="566652928"/>
-        <c:axId val="566654848"/>
+        <c:axId val="594492416"/>
+        <c:axId val="594678528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="566652928"/>
+        <c:axId val="594492416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14877,14 +15059,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566654848"/>
+        <c:crossAx val="594678528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="566654848"/>
+        <c:axId val="594678528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14935,7 +15117,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566652928"/>
+        <c:crossAx val="594492416"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15126,7 +15308,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15300,6 +15482,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-4638.4941455386206</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-23626.331525577141</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15319,8 +15504,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="429753856"/>
-        <c:axId val="429752320"/>
+        <c:axId val="444279040"/>
+        <c:axId val="444277504"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15345,7 +15530,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15519,6 +15704,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15528,7 +15716,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15702,6 +15890,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1.0479999780654907</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.1770000457763672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15723,11 +15914,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="429744896"/>
-        <c:axId val="429746432"/>
+        <c:axId val="444003840"/>
+        <c:axId val="444005376"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="429744896"/>
+        <c:axId val="444003840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15770,14 +15961,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="429746432"/>
+        <c:crossAx val="444005376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="429746432"/>
+        <c:axId val="444005376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15828,12 +16019,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="429744896"/>
+        <c:crossAx val="444003840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="429752320"/>
+        <c:axId val="444277504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15870,12 +16061,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="429753856"/>
+        <c:crossAx val="444279040"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="429753856"/>
+        <c:axId val="444279040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15884,7 +16075,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="429752320"/>
+        <c:crossAx val="444277504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16063,7 +16254,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16237,6 +16428,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16246,7 +16440,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16419,6 +16613,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -16462,7 +16659,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16636,6 +16833,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16645,7 +16845,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16819,6 +17019,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14318986.804726198</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>15963969.244530939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16861,7 +17064,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17035,6 +17238,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17044,7 +17250,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17218,6 +17424,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>4784917.2261552308</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6429899.665959971</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17239,11 +17448,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433320704"/>
-        <c:axId val="433322240"/>
+        <c:axId val="444327424"/>
+        <c:axId val="444328960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433320704"/>
+        <c:axId val="444327424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17286,14 +17495,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433322240"/>
+        <c:crossAx val="444328960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433322240"/>
+        <c:axId val="444328960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17344,7 +17553,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433320704"/>
+        <c:crossAx val="444327424"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18280,7 +18489,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18411,28 +18620,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -20845,6 +21054,44 @@
       </c>
       <c r="L60" s="29">
         <v>955105.75082399882</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="32">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="31">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="29">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="29">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="30">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="30">
+        <v>12243926.091061944</v>
+      </c>
+      <c r="H61" s="30">
+        <v>14411101.569662364</v>
+      </c>
+      <c r="I61" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J61" s="30">
+        <v>15638155.580985475</v>
+      </c>
+      <c r="K61" s="30">
+        <v>6276820.7632580511</v>
+      </c>
+      <c r="L61" s="29">
+        <v>1227054.0113231102</v>
       </c>
     </row>
   </sheetData>
@@ -20863,7 +21110,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -20901,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>3</v>
@@ -20934,16 +21181,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -21005,28 +21252,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -24104,6 +24351,56 @@
         <v>67.160806984825626</v>
       </c>
       <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-54389.65209982227</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-46210.40780329454</v>
+      </c>
+      <c r="G61" s="18">
+        <v>14824747.516673513</v>
+      </c>
+      <c r="H61" s="18">
+        <v>17448728.50574781</v>
+      </c>
+      <c r="I61" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J61" s="18">
+        <v>18043573.156056687</v>
+      </c>
+      <c r="K61" s="18">
+        <v>7155737.3825757094</v>
+      </c>
+      <c r="L61" s="17">
+        <v>594844.65030887653</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -24123,7 +24420,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH60"/>
+  <dimension ref="A1:AH61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24161,13 +24458,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -24194,16 +24491,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -24265,28 +24562,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27364,6 +27661,56 @@
         <v>67.160806984825626</v>
       </c>
       <c r="P60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-451295.36763222498</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-383428.50474108831</v>
+      </c>
+      <c r="G61" s="18">
+        <v>134465571.64963385</v>
+      </c>
+      <c r="H61" s="18">
+        <v>158265983.98696443</v>
+      </c>
+      <c r="I61" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J61" s="18">
+        <v>162087884.14543834</v>
+      </c>
+      <c r="K61" s="18">
+        <v>65939423.317233339</v>
+      </c>
+      <c r="L61" s="17">
+        <v>3821900.1584739117</v>
+      </c>
+      <c r="M61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="N61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="O61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="P61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -27383,7 +27730,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27430,10 +27777,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27460,16 +27807,16 @@
         <v>12</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="48" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -27543,28 +27890,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -30984,6 +31331,62 @@
         <v>67.160806984825626</v>
       </c>
       <c r="R60" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-23626.331525577141</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-20073.348009084275</v>
+      </c>
+      <c r="I61" s="18">
+        <v>19014878.838440388</v>
+      </c>
+      <c r="J61" s="18">
+        <v>22380513.263276413</v>
+      </c>
+      <c r="K61" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L61" s="18">
+        <v>22685429.809759744</v>
+      </c>
+      <c r="M61" s="18">
+        <v>10283133.329829985</v>
+      </c>
+      <c r="N61" s="17">
+        <v>304916.54648332909</v>
+      </c>
+      <c r="O61" s="22">
+        <v>3.8522502668723251E-2</v>
+      </c>
+      <c r="P61" s="22">
+        <v>4.6845882110407668E-2</v>
+      </c>
+      <c r="Q61" s="22">
+        <v>82.232420296691927</v>
+      </c>
+      <c r="R61" s="1">
         <v>0.2</v>
       </c>
     </row>
@@ -31003,7 +31406,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31041,13 +31444,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -31074,19 +31477,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N1" s="48" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O1" s="48" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="P1" s="48" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31164,28 +31567,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34437,6 +34840,59 @@
         <v>72.339479812190092</v>
       </c>
       <c r="Q60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-231052.03901647267</v>
+      </c>
+      <c r="G61" s="18">
+        <v>12520743.126638651</v>
+      </c>
+      <c r="H61" s="18">
+        <v>14736915.233207827</v>
+      </c>
+      <c r="I61" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J61" s="18">
+        <v>15963969.244530939</v>
+      </c>
+      <c r="K61" s="18">
+        <v>6429899.665959971</v>
+      </c>
+      <c r="L61" s="17">
+        <v>1227054.0113231102</v>
+      </c>
+      <c r="M61" s="21">
+        <v>96.011413524955756</v>
+      </c>
+      <c r="N61" s="21">
+        <v>83.590090588113569</v>
+      </c>
+      <c r="O61" s="21">
+        <v>81.129632711666943</v>
+      </c>
+      <c r="P61" s="21">
+        <v>88.511006341006805</v>
+      </c>
+      <c r="Q61" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34456,7 +34912,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ60"/>
+  <dimension ref="A1:AJ61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34494,19 +34950,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -34602,28 +35058,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -37378,6 +37834,50 @@
       </c>
       <c r="N60" s="17">
         <v>3385616.7575219027</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>1531906</v>
+      </c>
+      <c r="F61" s="17">
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="G61" s="17">
+        <v>-848400.08660027001</v>
+      </c>
+      <c r="H61" s="18">
+        <v>-720815.67850802618</v>
+      </c>
+      <c r="I61" s="18">
+        <v>117119825.98118354</v>
+      </c>
+      <c r="J61" s="18">
+        <v>137850040.54117319</v>
+      </c>
+      <c r="K61" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L61" s="18">
+        <v>142084057.38529536</v>
+      </c>
+      <c r="M61" s="18">
+        <v>64669351.234407663</v>
+      </c>
+      <c r="N61" s="17">
+        <v>4234016.8441221723</v>
       </c>
     </row>
   </sheetData>
@@ -37396,7 +37896,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37434,13 +37934,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -37527,28 +38027,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -39961,6 +40461,44 @@
       </c>
       <c r="L60" s="17">
         <v>5521925.9071746431</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B61" s="31">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="C61" s="16">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D61" s="17">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E61" s="17">
+        <v>-2256476.8381611248</v>
+      </c>
+      <c r="F61" s="18">
+        <v>-1917142.5237054415</v>
+      </c>
+      <c r="G61" s="18">
+        <v>111576016.41776104</v>
+      </c>
+      <c r="H61" s="18">
+        <v>131324976.43124944</v>
+      </c>
+      <c r="I61" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J61" s="18">
+        <v>139103379.1765852</v>
+      </c>
+      <c r="K61" s="18">
+        <v>57331541.7023485</v>
+      </c>
+      <c r="L61" s="17">
+        <v>7778402.745335768</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel4(RSI&KDJ)cn.xlsx
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="33">
   <si>
     <t>in practice</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -125,10 +125,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>每年投入本金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -146,6 +142,10 @@
   </si>
   <si>
     <t>年化收益率</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -174,10 +174,6 @@
   </si>
   <si>
     <t>标志</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>PE</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -667,7 +663,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -844,6 +840,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -853,7 +852,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1029,6 +1028,9 @@
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9361334.8177274242</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9361334.8177274242</c:v>
                 </c:pt>
               </c:numCache>
@@ -1072,7 +1074,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1249,6 +1251,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1258,7 +1263,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1435,6 +1440,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15638155.580985475</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16470742.053078819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1477,7 +1485,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1654,6 +1662,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1663,7 +1674,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1840,6 +1851,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6276820.7632580511</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7109407.2353513949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1861,11 +1875,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444378112"/>
-        <c:axId val="444380288"/>
+        <c:axId val="440983936"/>
+        <c:axId val="440985472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444378112"/>
+        <c:axId val="440983936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1908,14 +1922,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444380288"/>
+        <c:crossAx val="440985472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444380288"/>
+        <c:axId val="440985472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1966,7 +1980,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444378112"/>
+        <c:crossAx val="440983936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2157,7 +2171,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2334,6 +2348,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2353,8 +2370,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="467548800"/>
-        <c:axId val="467547264"/>
+        <c:axId val="495759744"/>
+        <c:axId val="495757952"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2379,7 +2396,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2556,6 +2573,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2565,7 +2585,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2742,6 +2762,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2763,11 +2786,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467543936"/>
-        <c:axId val="467545472"/>
+        <c:axId val="495750528"/>
+        <c:axId val="495756416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467543936"/>
+        <c:axId val="495750528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2810,14 +2833,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467545472"/>
+        <c:crossAx val="495756416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467545472"/>
+        <c:axId val="495756416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2868,12 +2891,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467543936"/>
+        <c:crossAx val="495750528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="467547264"/>
+        <c:axId val="495757952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2910,12 +2933,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467548800"/>
+        <c:crossAx val="495759744"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="467548800"/>
+        <c:axId val="495759744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2924,7 +2947,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="467547264"/>
+        <c:crossAx val="495757952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3103,7 +3126,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3280,6 +3303,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3289,7 +3315,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3465,6 +3491,9 @@
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>77414706.150887698</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>77414706.150887698</c:v>
                 </c:pt>
               </c:numCache>
@@ -3508,7 +3537,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -3685,6 +3714,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3694,7 +3726,7 @@
               <c:f>'模型四 (3)PE副本成交量'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3871,6 +3903,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>142084057.38529536</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>150048200.74916655</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3913,7 +3948,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4090,6 +4125,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4099,7 +4137,7 @@
               <c:f>'模型四 (3)PE副本成交量'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4276,6 +4314,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>64669351.234407663</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>72633494.59827885</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4297,11 +4338,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="487425920"/>
-        <c:axId val="487427456"/>
+        <c:axId val="497626496"/>
+        <c:axId val="497628288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="487425920"/>
+        <c:axId val="497626496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4344,14 +4385,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487427456"/>
+        <c:crossAx val="497628288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="487427456"/>
+        <c:axId val="497628288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4402,7 +4443,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487425920"/>
+        <c:crossAx val="497626496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4593,7 +4634,7 @@
               <c:f>'模型四 (3)PE副本成交量'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4770,6 +4811,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-848400.08660027001</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-2083411.4657620986</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4789,8 +4833,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="487455744"/>
-        <c:axId val="487454208"/>
+        <c:axId val="498574080"/>
+        <c:axId val="498564096"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4815,7 +4859,7 @@
               <c:f>'模型四 (3)PE副本成交量'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -4992,6 +5036,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5001,7 +5048,7 @@
               <c:f>'模型四 (3)PE副本成交量'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -5178,6 +5225,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5199,11 +5249,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="487450880"/>
-        <c:axId val="487452672"/>
+        <c:axId val="498561024"/>
+        <c:axId val="498562560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="487450880"/>
+        <c:axId val="498561024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5246,14 +5296,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487452672"/>
+        <c:crossAx val="498562560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="487452672"/>
+        <c:axId val="498562560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5304,12 +5354,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487450880"/>
+        <c:crossAx val="498561024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="487454208"/>
+        <c:axId val="498564096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5346,12 +5396,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="487455744"/>
+        <c:crossAx val="498574080"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="487455744"/>
+        <c:axId val="498574080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5360,7 +5410,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="487454208"/>
+        <c:crossAx val="498564096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5539,7 +5589,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -5716,6 +5766,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5725,7 +5778,7 @@
               <c:f>'模型四 (3)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5901,6 +5954,9 @@
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>81771837.474236697</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>81771837.474236697</c:v>
                 </c:pt>
               </c:numCache>
@@ -5944,7 +6000,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6121,6 +6177,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6130,7 +6189,7 @@
               <c:f>'模型四 (3)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6307,6 +6366,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>139103379.1765852</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>146690543.71748418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6349,7 +6411,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -6526,6 +6588,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6535,7 +6600,7 @@
               <c:f>'模型四 (3)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6712,6 +6777,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>57331541.7023485</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>64918706.243247479</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6733,11 +6801,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="489319040"/>
-        <c:axId val="489333120"/>
+        <c:axId val="498692096"/>
+        <c:axId val="498693632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="489319040"/>
+        <c:axId val="498692096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6780,14 +6848,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489333120"/>
+        <c:crossAx val="498693632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="489333120"/>
+        <c:axId val="498693632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6838,7 +6906,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489319040"/>
+        <c:crossAx val="498692096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7029,7 +7097,7 @@
               <c:f>'模型四 (3)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7206,6 +7274,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-2256476.8381611248</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-3004608.0591776534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7225,8 +7296,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529940480"/>
-        <c:axId val="489355520"/>
+        <c:axId val="498726016"/>
+        <c:axId val="498724224"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -7251,7 +7322,7 @@
               <c:f>'模型四 (3)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -7428,6 +7499,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7437,7 +7511,7 @@
               <c:f>'模型四 (3)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -7614,6 +7688,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7635,11 +7712,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="489352192"/>
-        <c:axId val="489353984"/>
+        <c:axId val="498721152"/>
+        <c:axId val="498722688"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="489352192"/>
+        <c:axId val="498721152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7682,14 +7759,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489353984"/>
+        <c:crossAx val="498722688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="489353984"/>
+        <c:axId val="498722688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7740,12 +7817,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489352192"/>
+        <c:crossAx val="498721152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="489355520"/>
+        <c:axId val="498724224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7782,12 +7859,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529940480"/>
+        <c:crossAx val="498726016"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529940480"/>
+        <c:axId val="498726016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7796,7 +7873,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="489355520"/>
+        <c:crossAx val="498724224"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7958,7 +8035,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8135,6 +8212,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8154,8 +8234,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="572200448"/>
-        <c:axId val="572197888"/>
+        <c:axId val="576074880"/>
+        <c:axId val="575946112"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -8180,7 +8260,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -8357,6 +8437,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8366,7 +8449,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -8543,6 +8626,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8564,11 +8650,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="562884992"/>
-        <c:axId val="562886528"/>
+        <c:axId val="575942656"/>
+        <c:axId val="575944576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="562884992"/>
+        <c:axId val="575942656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8611,14 +8697,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562886528"/>
+        <c:crossAx val="575944576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="562886528"/>
+        <c:axId val="575944576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8669,12 +8755,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="562884992"/>
+        <c:crossAx val="575942656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="572197888"/>
+        <c:axId val="575946112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8711,12 +8797,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572200448"/>
+        <c:crossAx val="576074880"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="572200448"/>
+        <c:axId val="576074880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8725,7 +8811,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="572197888"/>
+        <c:crossAx val="575946112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8904,7 +8990,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9081,6 +9167,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9090,7 +9179,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9266,6 +9355,9 @@
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>10887835.773480978</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>10887835.773480978</c:v>
                 </c:pt>
               </c:numCache>
@@ -9309,7 +9401,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9486,6 +9578,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9495,7 +9590,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9672,6 +9767,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>18043573.156056687</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19051655.379257303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9714,7 +9812,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -9891,6 +9989,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9900,7 +10001,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10077,6 +10178,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>7155737.3825757094</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>8163819.6057763249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10098,11 +10202,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="572288384"/>
-        <c:axId val="572298368"/>
+        <c:axId val="576258048"/>
+        <c:axId val="576259584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="572288384"/>
+        <c:axId val="576258048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10145,14 +10249,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572298368"/>
+        <c:crossAx val="576259584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="572298368"/>
+        <c:axId val="576259584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10203,7 +10307,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572288384"/>
+        <c:crossAx val="576258048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10415,7 +10519,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10592,6 +10696,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-54389.65209982227</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10611,8 +10718,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="573272832"/>
-        <c:axId val="573250176"/>
+        <c:axId val="576491520"/>
+        <c:axId val="576374656"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -10637,7 +10744,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -10814,6 +10921,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10823,7 +10933,7 @@
               <c:f>'模型四 (1)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -11000,6 +11110,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11021,11 +11134,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573233408"/>
-        <c:axId val="573247488"/>
+        <c:axId val="576370944"/>
+        <c:axId val="576373120"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573233408"/>
+        <c:axId val="576370944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11068,14 +11181,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573247488"/>
+        <c:crossAx val="576373120"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573247488"/>
+        <c:axId val="576373120"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11126,12 +11239,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573233408"/>
+        <c:crossAx val="576370944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="573250176"/>
+        <c:axId val="576374656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11168,12 +11281,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573272832"/>
+        <c:crossAx val="576491520"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="573272832"/>
+        <c:axId val="576491520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11182,7 +11295,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="573250176"/>
+        <c:crossAx val="576374656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11361,7 +11474,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11538,6 +11651,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11547,7 +11663,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11723,6 +11839,9 @@
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>96148460.828205004</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>96148460.828205004</c:v>
                 </c:pt>
               </c:numCache>
@@ -11766,7 +11885,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -11943,6 +12062,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11952,7 +12074,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12129,6 +12251,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>162087884.14543834</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>171231537.50344989</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12171,7 +12296,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -12348,6 +12473,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12357,7 +12485,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12534,6 +12662,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>65939423.317233339</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>75083076.675244883</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12555,11 +12686,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573526784"/>
-        <c:axId val="573528320"/>
+        <c:axId val="576538496"/>
+        <c:axId val="576540032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573526784"/>
+        <c:axId val="576538496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12602,14 +12733,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573528320"/>
+        <c:crossAx val="576540032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573528320"/>
+        <c:axId val="576540032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12660,7 +12791,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573526784"/>
+        <c:crossAx val="576538496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12872,7 +13003,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13049,6 +13180,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-451295.36763222498</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-3004608.0591776534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13068,8 +13202,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="573789312"/>
-        <c:axId val="573676928"/>
+        <c:axId val="577215872"/>
+        <c:axId val="577213184"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -13094,7 +13228,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13271,6 +13405,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13280,7 +13417,7 @@
               <c:f>'模型四 (3)PE副本计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -13457,6 +13594,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13478,11 +13618,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="573673472"/>
-        <c:axId val="573675392"/>
+        <c:axId val="577029248"/>
+        <c:axId val="577030784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="573673472"/>
+        <c:axId val="577029248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13525,14 +13665,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573675392"/>
+        <c:crossAx val="577030784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573675392"/>
+        <c:axId val="577030784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13583,12 +13723,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573673472"/>
+        <c:crossAx val="577029248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="573676928"/>
+        <c:axId val="577213184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13625,12 +13765,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573789312"/>
+        <c:crossAx val="577215872"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="573789312"/>
+        <c:axId val="577215872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13639,7 +13779,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="573676928"/>
+        <c:crossAx val="577213184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13818,7 +13958,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -13995,6 +14135,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14004,7 +14147,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14180,6 +14323,9 @@
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>12402296.479929758</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>12402296.479929758</c:v>
                 </c:pt>
               </c:numCache>
@@ -14223,7 +14369,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14400,6 +14546,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14409,7 +14558,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14586,6 +14735,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>22685429.809759744</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>23978440.791011624</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14628,7 +14780,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -14805,6 +14957,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14814,7 +14969,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14991,6 +15146,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>10283133.329829985</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>11576144.311081866</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15012,11 +15170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="594492416"/>
-        <c:axId val="594678528"/>
+        <c:axId val="480139904"/>
+        <c:axId val="480153984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="594492416"/>
+        <c:axId val="480139904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15059,14 +15217,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="594678528"/>
+        <c:crossAx val="480153984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="594678528"/>
+        <c:axId val="480153984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15117,7 +15275,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="594492416"/>
+        <c:crossAx val="480139904"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15308,7 +15466,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15485,6 +15643,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-23626.331525577141</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-290095.26738459605</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15504,8 +15665,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="444279040"/>
-        <c:axId val="444277504"/>
+        <c:axId val="495099904"/>
+        <c:axId val="495098112"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -15530,7 +15691,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -15707,6 +15868,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15716,7 +15880,7 @@
               <c:f>'模型四 (3)PE副本成交量计算RSI'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -15893,6 +16057,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1.1770000457763672</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2450000047683716</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15914,11 +16081,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444003840"/>
-        <c:axId val="444005376"/>
+        <c:axId val="495086592"/>
+        <c:axId val="495096576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444003840"/>
+        <c:axId val="495086592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15961,14 +16128,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444005376"/>
+        <c:crossAx val="495096576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444005376"/>
+        <c:axId val="495096576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16019,12 +16186,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444003840"/>
+        <c:crossAx val="495086592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="444277504"/>
+        <c:axId val="495098112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16061,12 +16228,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444279040"/>
+        <c:crossAx val="495099904"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="444279040"/>
+        <c:axId val="495099904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -16075,7 +16242,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="444277504"/>
+        <c:crossAx val="495098112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -16254,7 +16421,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16431,6 +16598,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16440,7 +16610,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16616,6 +16786,9 @@
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9534069.5785709675</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9534069.5785709675</c:v>
                 </c:pt>
               </c:numCache>
@@ -16659,7 +16832,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -16836,6 +17009,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16845,7 +17021,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17022,6 +17198,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>15963969.244530939</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>16815379.263691787</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17064,7 +17243,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -17241,6 +17420,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17250,7 +17432,7 @@
               <c:f>'模型四 (1)PE副本计算KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17427,6 +17609,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>6429899.665959971</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7281309.6851208191</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17448,11 +17633,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444327424"/>
-        <c:axId val="444328960"/>
+        <c:axId val="495733760"/>
+        <c:axId val="495739648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444327424"/>
+        <c:axId val="495733760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17495,14 +17680,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444328960"/>
+        <c:crossAx val="495739648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444328960"/>
+        <c:axId val="495739648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17553,7 +17738,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444327424"/>
+        <c:crossAx val="495733760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -18489,7 +18674,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="24" customWidth="1"/>
@@ -18620,28 +18805,28 @@
       </c>
       <c r="M3" s="27"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -21092,6 +21277,44 @@
       </c>
       <c r="L61" s="29">
         <v>1227054.0113231102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="32">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="31">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="29">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="29">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="30">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="30">
+        <v>11979550.373187648</v>
+      </c>
+      <c r="H62" s="30">
+        <v>14914540.271741569</v>
+      </c>
+      <c r="I62" s="30">
+        <v>9361334.8177274242</v>
+      </c>
+      <c r="J62" s="30">
+        <v>16470742.053078819</v>
+      </c>
+      <c r="K62" s="30">
+        <v>7109407.2353513949</v>
+      </c>
+      <c r="L62" s="29">
+        <v>1556201.7813372496</v>
       </c>
     </row>
   </sheetData>
@@ -21110,7 +21333,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -21145,16 +21368,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -21252,28 +21475,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -24402,6 +24625,56 @@
       </c>
       <c r="P61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>14560371.798799217</v>
+      </c>
+      <c r="H62" s="18">
+        <v>18127662.958934288</v>
+      </c>
+      <c r="I62" s="18">
+        <v>10887835.773480978</v>
+      </c>
+      <c r="J62" s="18">
+        <v>19051655.379257303</v>
+      </c>
+      <c r="K62" s="18">
+        <v>8163819.6057763249</v>
+      </c>
+      <c r="L62" s="17">
+        <v>923992.42032301589</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24420,7 +24693,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:AH61"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -24455,16 +24728,16 @@
   <sheetData>
     <row r="1" spans="1:34" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -24562,28 +24835,28 @@
       </c>
       <c r="M3" s="21"/>
       <c r="Q3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="46" t="s">
+      <c r="S3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="U3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="W3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="X3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Z3" s="42">
         <v>44561</v>
@@ -27712,6 +27985,56 @@
       </c>
       <c r="P61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-3004608.0591776534</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-2413339.7973252633</v>
+      </c>
+      <c r="G62" s="18">
+        <v>132052231.85230859</v>
+      </c>
+      <c r="H62" s="18">
+        <v>164405029.28579831</v>
+      </c>
+      <c r="I62" s="18">
+        <v>96148460.828205004</v>
+      </c>
+      <c r="J62" s="18">
+        <v>171231537.50344989</v>
+      </c>
+      <c r="K62" s="18">
+        <v>75083076.675244883</v>
+      </c>
+      <c r="L62" s="17">
+        <v>6826508.2176515646</v>
+      </c>
+      <c r="M62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="N62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="O62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="P62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27730,7 +28053,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -27765,22 +28088,22 @@
   <sheetData>
     <row r="1" spans="1:36" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -27890,28 +28213,28 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="22"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -31388,6 +31711,62 @@
       </c>
       <c r="R61" s="1">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-290095.26738459605</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-233008.24600283225</v>
+      </c>
+      <c r="I62" s="18">
+        <v>18781870.592437558</v>
+      </c>
+      <c r="J62" s="18">
+        <v>23383428.977143697</v>
+      </c>
+      <c r="K62" s="18">
+        <v>12402296.479929758</v>
+      </c>
+      <c r="L62" s="18">
+        <v>23978440.791011624</v>
+      </c>
+      <c r="M62" s="18">
+        <v>11576144.311081866</v>
+      </c>
+      <c r="N62" s="17">
+        <v>595011.8138679252</v>
+      </c>
+      <c r="O62" s="22">
+        <v>4.3435412055936783E-2</v>
+      </c>
+      <c r="P62" s="22">
+        <v>5.037156159067379E-2</v>
+      </c>
+      <c r="Q62" s="22">
+        <v>86.230028778736084</v>
+      </c>
+      <c r="R62" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -31406,7 +31785,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31444,13 +31823,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -31477,19 +31856,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="48" t="s">
+      <c r="O1" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="48" t="s">
+      <c r="P1" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="48" t="s">
+      <c r="Q1" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:36" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -31567,28 +31946,28 @@
         <v>1</v>
       </c>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -34893,6 +35272,59 @@
         <v>88.511006341006805</v>
       </c>
       <c r="Q61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-264375.71787429531</v>
+      </c>
+      <c r="G62" s="18">
+        <v>12256367.408764355</v>
+      </c>
+      <c r="H62" s="18">
+        <v>15259177.482354537</v>
+      </c>
+      <c r="I62" s="18">
+        <v>9534069.5785709675</v>
+      </c>
+      <c r="J62" s="18">
+        <v>16815379.263691787</v>
+      </c>
+      <c r="K62" s="18">
+        <v>7281309.6851208191</v>
+      </c>
+      <c r="L62" s="17">
+        <v>1556201.7813372496</v>
+      </c>
+      <c r="M62" s="21">
+        <v>93.931398043426469</v>
+      </c>
+      <c r="N62" s="21">
+        <v>87.037193073217864</v>
+      </c>
+      <c r="O62" s="21">
+        <v>83.098819498850574</v>
+      </c>
+      <c r="P62" s="21">
+        <v>94.913940221952458</v>
+      </c>
+      <c r="Q62" s="1">
         <v>1</v>
       </c>
     </row>
@@ -34912,7 +35344,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -34950,19 +35382,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>27</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>28</v>
       </c>
       <c r="G1" s="40" t="s">
         <v>5</v>
@@ -35058,28 +35490,28 @@
       </c>
       <c r="O3" s="7"/>
       <c r="S3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46" t="s">
+      <c r="U3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="U3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="V3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="W3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="Y3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="Z3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="AB3" s="42">
         <v>44561</v>
@@ -37878,6 +38310,50 @@
       </c>
       <c r="N61" s="17">
         <v>4234016.8441221723</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2806705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="G62" s="17">
+        <v>-2083411.4657620986</v>
+      </c>
+      <c r="H62" s="18">
+        <v>-1673422.857656704</v>
+      </c>
+      <c r="I62" s="18">
+        <v>115446403.12352684</v>
+      </c>
+      <c r="J62" s="18">
+        <v>143730772.43928227</v>
+      </c>
+      <c r="K62" s="18">
+        <v>77414706.150887698</v>
+      </c>
+      <c r="L62" s="18">
+        <v>150048200.74916655</v>
+      </c>
+      <c r="M62" s="18">
+        <v>72633494.59827885</v>
+      </c>
+      <c r="N62" s="17">
+        <v>6317428.3098842707</v>
       </c>
     </row>
   </sheetData>
@@ -37896,7 +38372,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37931,16 +38407,16 @@
   <sheetData>
     <row r="1" spans="1:33" s="11" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E1" s="40" t="s">
         <v>5</v>
@@ -38027,28 +38503,28 @@
       </c>
       <c r="M3" s="7"/>
       <c r="P3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="R3" s="46" t="s">
         <v>14</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>15</v>
       </c>
       <c r="S3" s="46" t="s">
         <v>10</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U3" s="47" t="s">
         <v>12</v>
       </c>
       <c r="V3" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="46" t="s">
         <v>17</v>
-      </c>
-      <c r="W3" s="46" t="s">
-        <v>18</v>
       </c>
       <c r="Y3" s="42">
         <v>44561</v>
@@ -40499,6 +40975,44 @@
       </c>
       <c r="L61" s="17">
         <v>7778402.745335768</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B62" s="31">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="C62" s="16">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D62" s="17">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E62" s="17">
+        <v>-3004608.0591776534</v>
+      </c>
+      <c r="F62" s="18">
+        <v>-2413339.7973252633</v>
+      </c>
+      <c r="G62" s="18">
+        <v>109162676.62043577</v>
+      </c>
+      <c r="H62" s="18">
+        <v>135907532.91297075</v>
+      </c>
+      <c r="I62" s="18">
+        <v>81771837.474236697</v>
+      </c>
+      <c r="J62" s="18">
+        <v>146690543.71748418</v>
+      </c>
+      <c r="K62" s="18">
+        <v>64918706.243247479</v>
+      </c>
+      <c r="L62" s="17">
+        <v>10783010.804513421</v>
       </c>
     </row>
   </sheetData>
